--- a/public/templates/SALES_TEMU_TEMPLATE.xlsx
+++ b/public/templates/SALES_TEMU_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -47,19 +47,31 @@
     <t>Commission</t>
   </si>
   <si>
+    <t>Commission VAT</t>
+  </si>
+  <si>
     <t>Postage</t>
   </si>
   <si>
+    <t>P. VAT</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t>Total VAT</t>
+  </si>
+  <si>
     <t>GP</t>
   </si>
   <si>
     <t>GP %</t>
   </si>
   <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
+    <t>Total VAT NTP</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>PO-210-07053322437751959</t>
@@ -581,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -589,12 +601,14 @@
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="16" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
-    <col min="10" max="12" width="16" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="10" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,56 +654,80 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2">
-        <v>119.33</v>
+        <v>83.99</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K2" s="2">
+        <v>3.87</v>
       </c>
       <c r="L2" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="M2" s="2">
         <v>6.3</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:S1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -711,46 +749,46 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -758,13 +796,13 @@
         <v>0</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,13 +810,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -800,13 +838,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -814,13 +852,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -828,13 +866,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -842,41 +880,41 @@
         <v>7</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/SALES_TEMU_TEMPLATE.xlsx
+++ b/public/templates/SALES_TEMU_TEMPLATE.xlsx
@@ -101,16 +101,16 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>TEMU-EXAMPLE</t>
+    <t>PO-210-07053322437751959</t>
   </si>
   <si>
     <t>SG-A17-128GB-OB</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350901801557294</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>MHL</t>
   </si>
   <si>
     <t/>

--- a/public/templates/SALES_TEMU_TEMPLATE.xlsx
+++ b/public/templates/SALES_TEMU_TEMPLATE.xlsx
@@ -779,37 +779,37 @@
         <v>83.99</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
         <v>3.87</v>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",K2*20%)</f>
+        <f>K2*20%</f>
       </c>
       <c r="M2" s="3">
         <v>6.3</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>1</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",N2)</f>
+        <f>N2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($H2="","",I2-J2-K2-M2-N2-O2)</f>
+        <f>I2-J2-K2-M2-N2-O2</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",(Q2-Z2)/G2*100)</f>
+        <f>(Q2-Z2)/G2*100</f>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",J2-P2)</f>
+        <f>J2-P2</f>
       </c>
       <c r="T2" t="s">
         <v>33</v>
@@ -818,7 +818,7 @@
         <v>34</v>
       </c>
       <c r="AA2" s="3">
-        <f>IF($H2="","",Q2-Z2)</f>
+        <f>Q2-Z2</f>
       </c>
       <c r="AB2" t="s">
         <v>33</v>
@@ -827,7 +827,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -865,7 +865,7 @@
         <f>IF($H3="","",Q3-Z3)</f>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -903,7 +903,7 @@
         <f>IF($H4="","",Q4-Z4)</f>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -941,7 +941,7 @@
         <f>IF($H5="","",Q5-Z5)</f>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -979,7 +979,7 @@
         <f>IF($H6="","",Q6-Z6)</f>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -1017,7 +1017,7 @@
         <f>IF($H7="","",Q7-Z7)</f>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -1055,7 +1055,7 @@
         <f>IF($H8="","",Q8-Z8)</f>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -1093,7 +1093,7 @@
         <f>IF($H9="","",Q9-Z9)</f>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -1131,7 +1131,7 @@
         <f>IF($H10="","",Q10-Z10)</f>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -1169,7 +1169,7 @@
         <f>IF($H11="","",Q11-Z11)</f>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -1207,7 +1207,7 @@
         <f>IF($H12="","",Q12-Z12)</f>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -1245,7 +1245,7 @@
         <f>IF($H13="","",Q13-Z13)</f>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -1283,7 +1283,7 @@
         <f>IF($H14="","",Q14-Z14)</f>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -1321,7 +1321,7 @@
         <f>IF($H15="","",Q15-Z15)</f>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -1359,7 +1359,7 @@
         <f>IF($H16="","",Q16-Z16)</f>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -1397,7 +1397,7 @@
         <f>IF($H17="","",Q17-Z17)</f>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -1435,7 +1435,7 @@
         <f>IF($H18="","",Q18-Z18)</f>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -1473,7 +1473,7 @@
         <f>IF($H19="","",Q19-Z19)</f>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -1511,7 +1511,7 @@
         <f>IF($H20="","",Q20-Z20)</f>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -1549,7 +1549,7 @@
         <f>IF($H21="","",Q21-Z21)</f>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -1587,7 +1587,7 @@
         <f>IF($H22="","",Q22-Z22)</f>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -1625,7 +1625,7 @@
         <f>IF($H23="","",Q23-Z23)</f>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -1663,7 +1663,7 @@
         <f>IF($H24="","",Q24-Z24)</f>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -1701,7 +1701,7 @@
         <f>IF($H25="","",Q25-Z25)</f>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -1739,7 +1739,7 @@
         <f>IF($H26="","",Q26-Z26)</f>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -1777,7 +1777,7 @@
         <f>IF($H27="","",Q27-Z27)</f>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -1815,7 +1815,7 @@
         <f>IF($H28="","",Q28-Z28)</f>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -1853,7 +1853,7 @@
         <f>IF($H29="","",Q29-Z29)</f>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -1891,7 +1891,7 @@
         <f>IF($H30="","",Q30-Z30)</f>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -1929,7 +1929,7 @@
         <f>IF($H31="","",Q31-Z31)</f>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -1967,7 +1967,7 @@
         <f>IF($H32="","",Q32-Z32)</f>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -2005,7 +2005,7 @@
         <f>IF($H33="","",Q33-Z33)</f>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -2043,7 +2043,7 @@
         <f>IF($H34="","",Q34-Z34)</f>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -2081,7 +2081,7 @@
         <f>IF($H35="","",Q35-Z35)</f>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -2119,7 +2119,7 @@
         <f>IF($H36="","",Q36-Z36)</f>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -2157,7 +2157,7 @@
         <f>IF($H37="","",Q37-Z37)</f>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -2195,7 +2195,7 @@
         <f>IF($H38="","",Q38-Z38)</f>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -2233,7 +2233,7 @@
         <f>IF($H39="","",Q39-Z39)</f>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -2271,7 +2271,7 @@
         <f>IF($H40="","",Q40-Z40)</f>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -2309,7 +2309,7 @@
         <f>IF($H41="","",Q41-Z41)</f>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -2347,7 +2347,7 @@
         <f>IF($H42="","",Q42-Z42)</f>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -2385,7 +2385,7 @@
         <f>IF($H43="","",Q43-Z43)</f>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -2423,7 +2423,7 @@
         <f>IF($H44="","",Q44-Z44)</f>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -2461,7 +2461,7 @@
         <f>IF($H45="","",Q45-Z45)</f>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -2499,7 +2499,7 @@
         <f>IF($H46="","",Q46-Z46)</f>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -2537,7 +2537,7 @@
         <f>IF($H47="","",Q47-Z47)</f>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -2575,7 +2575,7 @@
         <f>IF($H48="","",Q48-Z48)</f>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -2613,7 +2613,7 @@
         <f>IF($H49="","",Q49-Z49)</f>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -2651,7 +2651,7 @@
         <f>IF($H50="","",Q50-Z50)</f>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -2689,7 +2689,7 @@
         <f>IF($H51="","",Q51-Z51)</f>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -2727,7 +2727,7 @@
         <f>IF($H52="","",Q52-Z52)</f>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -2765,7 +2765,7 @@
         <f>IF($H53="","",Q53-Z53)</f>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -2803,7 +2803,7 @@
         <f>IF($H54="","",Q54-Z54)</f>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -2841,7 +2841,7 @@
         <f>IF($H55="","",Q55-Z55)</f>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -2879,7 +2879,7 @@
         <f>IF($H56="","",Q56-Z56)</f>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -2917,7 +2917,7 @@
         <f>IF($H57="","",Q57-Z57)</f>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -2955,7 +2955,7 @@
         <f>IF($H58="","",Q58-Z58)</f>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -2993,7 +2993,7 @@
         <f>IF($H59="","",Q59-Z59)</f>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -3031,7 +3031,7 @@
         <f>IF($H60="","",Q60-Z60)</f>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -3069,7 +3069,7 @@
         <f>IF($H61="","",Q61-Z61)</f>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -3107,7 +3107,7 @@
         <f>IF($H62="","",Q62-Z62)</f>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -3145,7 +3145,7 @@
         <f>IF($H63="","",Q63-Z63)</f>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -3183,7 +3183,7 @@
         <f>IF($H64="","",Q64-Z64)</f>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -3221,7 +3221,7 @@
         <f>IF($H65="","",Q65-Z65)</f>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -3259,7 +3259,7 @@
         <f>IF($H66="","",Q66-Z66)</f>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -3297,7 +3297,7 @@
         <f>IF($H67="","",Q67-Z67)</f>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -3335,7 +3335,7 @@
         <f>IF($H68="","",Q68-Z68)</f>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -3373,7 +3373,7 @@
         <f>IF($H69="","",Q69-Z69)</f>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -3411,7 +3411,7 @@
         <f>IF($H70="","",Q70-Z70)</f>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -3449,7 +3449,7 @@
         <f>IF($H71="","",Q71-Z71)</f>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -3487,7 +3487,7 @@
         <f>IF($H72="","",Q72-Z72)</f>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -3525,7 +3525,7 @@
         <f>IF($H73="","",Q73-Z73)</f>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -3563,7 +3563,7 @@
         <f>IF($H74="","",Q74-Z74)</f>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -3601,7 +3601,7 @@
         <f>IF($H75="","",Q75-Z75)</f>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -3639,7 +3639,7 @@
         <f>IF($H76="","",Q76-Z76)</f>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -3677,7 +3677,7 @@
         <f>IF($H77="","",Q77-Z77)</f>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -3715,7 +3715,7 @@
         <f>IF($H78="","",Q78-Z78)</f>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -3753,7 +3753,7 @@
         <f>IF($H79="","",Q79-Z79)</f>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -3791,7 +3791,7 @@
         <f>IF($H80="","",Q80-Z80)</f>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -3829,7 +3829,7 @@
         <f>IF($H81="","",Q81-Z81)</f>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -3867,7 +3867,7 @@
         <f>IF($H82="","",Q82-Z82)</f>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -3905,7 +3905,7 @@
         <f>IF($H83="","",Q83-Z83)</f>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -3943,7 +3943,7 @@
         <f>IF($H84="","",Q84-Z84)</f>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -3981,7 +3981,7 @@
         <f>IF($H85="","",Q85-Z85)</f>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -4019,7 +4019,7 @@
         <f>IF($H86="","",Q86-Z86)</f>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -4057,7 +4057,7 @@
         <f>IF($H87="","",Q87-Z87)</f>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -4095,7 +4095,7 @@
         <f>IF($H88="","",Q88-Z88)</f>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -4133,7 +4133,7 @@
         <f>IF($H89="","",Q89-Z89)</f>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -4171,7 +4171,7 @@
         <f>IF($H90="","",Q90-Z90)</f>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -4209,7 +4209,7 @@
         <f>IF($H91="","",Q91-Z91)</f>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -4247,7 +4247,7 @@
         <f>IF($H92="","",Q92-Z92)</f>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -4285,7 +4285,7 @@
         <f>IF($H93="","",Q93-Z93)</f>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -4323,7 +4323,7 @@
         <f>IF($H94="","",Q94-Z94)</f>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -4361,7 +4361,7 @@
         <f>IF($H95="","",Q95-Z95)</f>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -4399,7 +4399,7 @@
         <f>IF($H96="","",Q96-Z96)</f>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -4437,7 +4437,7 @@
         <f>IF($H97="","",Q97-Z97)</f>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -4475,7 +4475,7 @@
         <f>IF($H98="","",Q98-Z98)</f>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -4513,7 +4513,7 @@
         <f>IF($H99="","",Q99-Z99)</f>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -4551,7 +4551,7 @@
         <f>IF($H100="","",Q100-Z100)</f>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -4589,7 +4589,7 @@
         <f>IF($H101="","",Q101-Z101)</f>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -4627,7 +4627,7 @@
         <f>IF($H102="","",Q102-Z102)</f>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -4665,7 +4665,7 @@
         <f>IF($H103="","",Q103-Z103)</f>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -4703,7 +4703,7 @@
         <f>IF($H104="","",Q104-Z104)</f>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -4741,7 +4741,7 @@
         <f>IF($H105="","",Q105-Z105)</f>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -4779,7 +4779,7 @@
         <f>IF($H106="","",Q106-Z106)</f>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -4817,7 +4817,7 @@
         <f>IF($H107="","",Q107-Z107)</f>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -4855,7 +4855,7 @@
         <f>IF($H108="","",Q108-Z108)</f>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -4893,7 +4893,7 @@
         <f>IF($H109="","",Q109-Z109)</f>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -4931,7 +4931,7 @@
         <f>IF($H110="","",Q110-Z110)</f>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -4969,7 +4969,7 @@
         <f>IF($H111="","",Q111-Z111)</f>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -5007,7 +5007,7 @@
         <f>IF($H112="","",Q112-Z112)</f>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -5045,7 +5045,7 @@
         <f>IF($H113="","",Q113-Z113)</f>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -5083,7 +5083,7 @@
         <f>IF($H114="","",Q114-Z114)</f>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -5121,7 +5121,7 @@
         <f>IF($H115="","",Q115-Z115)</f>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -5159,7 +5159,7 @@
         <f>IF($H116="","",Q116-Z116)</f>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -5197,7 +5197,7 @@
         <f>IF($H117="","",Q117-Z117)</f>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -5235,7 +5235,7 @@
         <f>IF($H118="","",Q118-Z118)</f>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -5273,7 +5273,7 @@
         <f>IF($H119="","",Q119-Z119)</f>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -5311,7 +5311,7 @@
         <f>IF($H120="","",Q120-Z120)</f>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -5349,7 +5349,7 @@
         <f>IF($H121="","",Q121-Z121)</f>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -5387,7 +5387,7 @@
         <f>IF($H122="","",Q122-Z122)</f>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -5425,7 +5425,7 @@
         <f>IF($H123="","",Q123-Z123)</f>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -5463,7 +5463,7 @@
         <f>IF($H124="","",Q124-Z124)</f>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -5501,7 +5501,7 @@
         <f>IF($H125="","",Q125-Z125)</f>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -5539,7 +5539,7 @@
         <f>IF($H126="","",Q126-Z126)</f>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -5577,7 +5577,7 @@
         <f>IF($H127="","",Q127-Z127)</f>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -5615,7 +5615,7 @@
         <f>IF($H128="","",Q128-Z128)</f>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -5653,7 +5653,7 @@
         <f>IF($H129="","",Q129-Z129)</f>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -5691,7 +5691,7 @@
         <f>IF($H130="","",Q130-Z130)</f>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -5729,7 +5729,7 @@
         <f>IF($H131="","",Q131-Z131)</f>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -5767,7 +5767,7 @@
         <f>IF($H132="","",Q132-Z132)</f>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -5805,7 +5805,7 @@
         <f>IF($H133="","",Q133-Z133)</f>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -5843,7 +5843,7 @@
         <f>IF($H134="","",Q134-Z134)</f>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -5881,7 +5881,7 @@
         <f>IF($H135="","",Q135-Z135)</f>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -5919,7 +5919,7 @@
         <f>IF($H136="","",Q136-Z136)</f>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -5957,7 +5957,7 @@
         <f>IF($H137="","",Q137-Z137)</f>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -5995,7 +5995,7 @@
         <f>IF($H138="","",Q138-Z138)</f>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -6033,7 +6033,7 @@
         <f>IF($H139="","",Q139-Z139)</f>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -6071,7 +6071,7 @@
         <f>IF($H140="","",Q140-Z140)</f>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -6109,7 +6109,7 @@
         <f>IF($H141="","",Q141-Z141)</f>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -6147,7 +6147,7 @@
         <f>IF($H142="","",Q142-Z142)</f>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -6185,7 +6185,7 @@
         <f>IF($H143="","",Q143-Z143)</f>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -6223,7 +6223,7 @@
         <f>IF($H144="","",Q144-Z144)</f>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -6261,7 +6261,7 @@
         <f>IF($H145="","",Q145-Z145)</f>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -6299,7 +6299,7 @@
         <f>IF($H146="","",Q146-Z146)</f>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -6337,7 +6337,7 @@
         <f>IF($H147="","",Q147-Z147)</f>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -6375,7 +6375,7 @@
         <f>IF($H148="","",Q148-Z148)</f>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -6413,7 +6413,7 @@
         <f>IF($H149="","",Q149-Z149)</f>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -6451,7 +6451,7 @@
         <f>IF($H150="","",Q150-Z150)</f>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -6489,7 +6489,7 @@
         <f>IF($H151="","",Q151-Z151)</f>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -6527,7 +6527,7 @@
         <f>IF($H152="","",Q152-Z152)</f>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -6565,7 +6565,7 @@
         <f>IF($H153="","",Q153-Z153)</f>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -6603,7 +6603,7 @@
         <f>IF($H154="","",Q154-Z154)</f>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -6641,7 +6641,7 @@
         <f>IF($H155="","",Q155-Z155)</f>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -6679,7 +6679,7 @@
         <f>IF($H156="","",Q156-Z156)</f>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -6717,7 +6717,7 @@
         <f>IF($H157="","",Q157-Z157)</f>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -6755,7 +6755,7 @@
         <f>IF($H158="","",Q158-Z158)</f>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -6793,7 +6793,7 @@
         <f>IF($H159="","",Q159-Z159)</f>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -6831,7 +6831,7 @@
         <f>IF($H160="","",Q160-Z160)</f>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -6869,7 +6869,7 @@
         <f>IF($H161="","",Q161-Z161)</f>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -6907,7 +6907,7 @@
         <f>IF($H162="","",Q162-Z162)</f>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -6945,7 +6945,7 @@
         <f>IF($H163="","",Q163-Z163)</f>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -6983,7 +6983,7 @@
         <f>IF($H164="","",Q164-Z164)</f>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -7021,7 +7021,7 @@
         <f>IF($H165="","",Q165-Z165)</f>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -7059,7 +7059,7 @@
         <f>IF($H166="","",Q166-Z166)</f>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -7097,7 +7097,7 @@
         <f>IF($H167="","",Q167-Z167)</f>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -7135,7 +7135,7 @@
         <f>IF($H168="","",Q168-Z168)</f>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -7173,7 +7173,7 @@
         <f>IF($H169="","",Q169-Z169)</f>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -7211,7 +7211,7 @@
         <f>IF($H170="","",Q170-Z170)</f>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -7249,7 +7249,7 @@
         <f>IF($H171="","",Q171-Z171)</f>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -7287,7 +7287,7 @@
         <f>IF($H172="","",Q172-Z172)</f>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -7325,7 +7325,7 @@
         <f>IF($H173="","",Q173-Z173)</f>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -7363,7 +7363,7 @@
         <f>IF($H174="","",Q174-Z174)</f>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -7401,7 +7401,7 @@
         <f>IF($H175="","",Q175-Z175)</f>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -7439,7 +7439,7 @@
         <f>IF($H176="","",Q176-Z176)</f>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -7477,7 +7477,7 @@
         <f>IF($H177="","",Q177-Z177)</f>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -7515,7 +7515,7 @@
         <f>IF($H178="","",Q178-Z178)</f>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -7553,7 +7553,7 @@
         <f>IF($H179="","",Q179-Z179)</f>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -7591,7 +7591,7 @@
         <f>IF($H180="","",Q180-Z180)</f>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -7629,7 +7629,7 @@
         <f>IF($H181="","",Q181-Z181)</f>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -7667,7 +7667,7 @@
         <f>IF($H182="","",Q182-Z182)</f>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -7705,7 +7705,7 @@
         <f>IF($H183="","",Q183-Z183)</f>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -7743,7 +7743,7 @@
         <f>IF($H184="","",Q184-Z184)</f>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -7781,7 +7781,7 @@
         <f>IF($H185="","",Q185-Z185)</f>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -7819,7 +7819,7 @@
         <f>IF($H186="","",Q186-Z186)</f>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -7857,7 +7857,7 @@
         <f>IF($H187="","",Q187-Z187)</f>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -7895,7 +7895,7 @@
         <f>IF($H188="","",Q188-Z188)</f>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -7933,7 +7933,7 @@
         <f>IF($H189="","",Q189-Z189)</f>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -7971,7 +7971,7 @@
         <f>IF($H190="","",Q190-Z190)</f>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -8009,7 +8009,7 @@
         <f>IF($H191="","",Q191-Z191)</f>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -8047,7 +8047,7 @@
         <f>IF($H192="","",Q192-Z192)</f>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -8085,7 +8085,7 @@
         <f>IF($H193="","",Q193-Z193)</f>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -8123,7 +8123,7 @@
         <f>IF($H194="","",Q194-Z194)</f>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -8161,7 +8161,7 @@
         <f>IF($H195="","",Q195-Z195)</f>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -8199,7 +8199,7 @@
         <f>IF($H196="","",Q196-Z196)</f>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -8237,7 +8237,7 @@
         <f>IF($H197="","",Q197-Z197)</f>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -8275,7 +8275,7 @@
         <f>IF($H198="","",Q198-Z198)</f>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -8313,7 +8313,7 @@
         <f>IF($H199="","",Q199-Z199)</f>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -8351,7 +8351,7 @@
         <f>IF($H200="","",Q200-Z200)</f>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -8389,7 +8389,7 @@
         <f>IF($H201="","",Q201-Z201)</f>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>

--- a/public/templates/SALES_TEMU_TEMPLATE.xlsx
+++ b/public/templates/SALES_TEMU_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -586,74 +598,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -664,10 +676,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD203"/>
+  <dimension ref="A1:AH203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,31 +770,43 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -800,7 +824,7 @@
         <f>L2*16.67%</f>
       </c>
       <c r="N2" s="3">
-        <f>K2*3.96%</f>
+        <f>K2*4.61%</f>
       </c>
       <c r="O2" s="3">
         <f>N2*20%</f>
@@ -824,19 +848,19 @@
         <f>L2-M2-N2-Q2-R2-S2</f>
       </c>
       <c r="V2" s="3">
-        <f>(U2-X2)/J2*100</f>
+        <f>(U2-AB2)/J2*100</f>
       </c>
       <c r="W2" s="3">
         <f>M2-T2</f>
       </c>
-      <c r="Y2" s="3">
-        <f>U2-X2</f>
-      </c>
-      <c r="AD2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC2" s="3">
+        <f>U2-AB2</f>
+      </c>
+      <c r="AH2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="J3" s="3"/>
@@ -870,16 +894,16 @@
         <f>IF($K3="","",L3-M3-N3-Q3-R3-S3)</f>
       </c>
       <c r="V3" s="3">
-        <f>IF($K3="","",(U3-X3)/J3*100)</f>
+        <f>IF($K3="","",(U3-AB3)/J3*100)</f>
       </c>
       <c r="W3" s="3">
         <f>IF($K3="","",M3-T3)</f>
       </c>
-      <c r="Y3" s="3">
-        <f>IF($K3="","",U3-X3)</f>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC3" s="3">
+        <f>IF($K3="","",U3-AB3)</f>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="J4" s="3"/>
@@ -913,16 +937,16 @@
         <f>IF($K4="","",L4-M4-N4-Q4-R4-S4)</f>
       </c>
       <c r="V4" s="3">
-        <f>IF($K4="","",(U4-X4)/J4*100)</f>
+        <f>IF($K4="","",(U4-AB4)/J4*100)</f>
       </c>
       <c r="W4" s="3">
         <f>IF($K4="","",M4-T4)</f>
       </c>
-      <c r="Y4" s="3">
-        <f>IF($K4="","",U4-X4)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC4" s="3">
+        <f>IF($K4="","",U4-AB4)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="J5" s="3"/>
@@ -956,16 +980,16 @@
         <f>IF($K5="","",L5-M5-N5-Q5-R5-S5)</f>
       </c>
       <c r="V5" s="3">
-        <f>IF($K5="","",(U5-X5)/J5*100)</f>
+        <f>IF($K5="","",(U5-AB5)/J5*100)</f>
       </c>
       <c r="W5" s="3">
         <f>IF($K5="","",M5-T5)</f>
       </c>
-      <c r="Y5" s="3">
-        <f>IF($K5="","",U5-X5)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC5" s="3">
+        <f>IF($K5="","",U5-AB5)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="J6" s="3"/>
@@ -999,16 +1023,16 @@
         <f>IF($K6="","",L6-M6-N6-Q6-R6-S6)</f>
       </c>
       <c r="V6" s="3">
-        <f>IF($K6="","",(U6-X6)/J6*100)</f>
+        <f>IF($K6="","",(U6-AB6)/J6*100)</f>
       </c>
       <c r="W6" s="3">
         <f>IF($K6="","",M6-T6)</f>
       </c>
-      <c r="Y6" s="3">
-        <f>IF($K6="","",U6-X6)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC6" s="3">
+        <f>IF($K6="","",U6-AB6)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="J7" s="3"/>
@@ -1042,16 +1066,16 @@
         <f>IF($K7="","",L7-M7-N7-Q7-R7-S7)</f>
       </c>
       <c r="V7" s="3">
-        <f>IF($K7="","",(U7-X7)/J7*100)</f>
+        <f>IF($K7="","",(U7-AB7)/J7*100)</f>
       </c>
       <c r="W7" s="3">
         <f>IF($K7="","",M7-T7)</f>
       </c>
-      <c r="Y7" s="3">
-        <f>IF($K7="","",U7-X7)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC7" s="3">
+        <f>IF($K7="","",U7-AB7)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="J8" s="3"/>
@@ -1085,16 +1109,16 @@
         <f>IF($K8="","",L8-M8-N8-Q8-R8-S8)</f>
       </c>
       <c r="V8" s="3">
-        <f>IF($K8="","",(U8-X8)/J8*100)</f>
+        <f>IF($K8="","",(U8-AB8)/J8*100)</f>
       </c>
       <c r="W8" s="3">
         <f>IF($K8="","",M8-T8)</f>
       </c>
-      <c r="Y8" s="3">
-        <f>IF($K8="","",U8-X8)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC8" s="3">
+        <f>IF($K8="","",U8-AB8)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="J9" s="3"/>
@@ -1128,16 +1152,16 @@
         <f>IF($K9="","",L9-M9-N9-Q9-R9-S9)</f>
       </c>
       <c r="V9" s="3">
-        <f>IF($K9="","",(U9-X9)/J9*100)</f>
+        <f>IF($K9="","",(U9-AB9)/J9*100)</f>
       </c>
       <c r="W9" s="3">
         <f>IF($K9="","",M9-T9)</f>
       </c>
-      <c r="Y9" s="3">
-        <f>IF($K9="","",U9-X9)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC9" s="3">
+        <f>IF($K9="","",U9-AB9)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="J10" s="3"/>
@@ -1171,16 +1195,16 @@
         <f>IF($K10="","",L10-M10-N10-Q10-R10-S10)</f>
       </c>
       <c r="V10" s="3">
-        <f>IF($K10="","",(U10-X10)/J10*100)</f>
+        <f>IF($K10="","",(U10-AB10)/J10*100)</f>
       </c>
       <c r="W10" s="3">
         <f>IF($K10="","",M10-T10)</f>
       </c>
-      <c r="Y10" s="3">
-        <f>IF($K10="","",U10-X10)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC10" s="3">
+        <f>IF($K10="","",U10-AB10)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="J11" s="3"/>
@@ -1214,16 +1238,16 @@
         <f>IF($K11="","",L11-M11-N11-Q11-R11-S11)</f>
       </c>
       <c r="V11" s="3">
-        <f>IF($K11="","",(U11-X11)/J11*100)</f>
+        <f>IF($K11="","",(U11-AB11)/J11*100)</f>
       </c>
       <c r="W11" s="3">
         <f>IF($K11="","",M11-T11)</f>
       </c>
-      <c r="Y11" s="3">
-        <f>IF($K11="","",U11-X11)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC11" s="3">
+        <f>IF($K11="","",U11-AB11)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="J12" s="3"/>
@@ -1257,16 +1281,16 @@
         <f>IF($K12="","",L12-M12-N12-Q12-R12-S12)</f>
       </c>
       <c r="V12" s="3">
-        <f>IF($K12="","",(U12-X12)/J12*100)</f>
+        <f>IF($K12="","",(U12-AB12)/J12*100)</f>
       </c>
       <c r="W12" s="3">
         <f>IF($K12="","",M12-T12)</f>
       </c>
-      <c r="Y12" s="3">
-        <f>IF($K12="","",U12-X12)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC12" s="3">
+        <f>IF($K12="","",U12-AB12)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="J13" s="3"/>
@@ -1300,16 +1324,16 @@
         <f>IF($K13="","",L13-M13-N13-Q13-R13-S13)</f>
       </c>
       <c r="V13" s="3">
-        <f>IF($K13="","",(U13-X13)/J13*100)</f>
+        <f>IF($K13="","",(U13-AB13)/J13*100)</f>
       </c>
       <c r="W13" s="3">
         <f>IF($K13="","",M13-T13)</f>
       </c>
-      <c r="Y13" s="3">
-        <f>IF($K13="","",U13-X13)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC13" s="3">
+        <f>IF($K13="","",U13-AB13)</f>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="J14" s="3"/>
@@ -1343,16 +1367,16 @@
         <f>IF($K14="","",L14-M14-N14-Q14-R14-S14)</f>
       </c>
       <c r="V14" s="3">
-        <f>IF($K14="","",(U14-X14)/J14*100)</f>
+        <f>IF($K14="","",(U14-AB14)/J14*100)</f>
       </c>
       <c r="W14" s="3">
         <f>IF($K14="","",M14-T14)</f>
       </c>
-      <c r="Y14" s="3">
-        <f>IF($K14="","",U14-X14)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC14" s="3">
+        <f>IF($K14="","",U14-AB14)</f>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="J15" s="3"/>
@@ -1386,16 +1410,16 @@
         <f>IF($K15="","",L15-M15-N15-Q15-R15-S15)</f>
       </c>
       <c r="V15" s="3">
-        <f>IF($K15="","",(U15-X15)/J15*100)</f>
+        <f>IF($K15="","",(U15-AB15)/J15*100)</f>
       </c>
       <c r="W15" s="3">
         <f>IF($K15="","",M15-T15)</f>
       </c>
-      <c r="Y15" s="3">
-        <f>IF($K15="","",U15-X15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC15" s="3">
+        <f>IF($K15="","",U15-AB15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="J16" s="3"/>
@@ -1429,16 +1453,16 @@
         <f>IF($K16="","",L16-M16-N16-Q16-R16-S16)</f>
       </c>
       <c r="V16" s="3">
-        <f>IF($K16="","",(U16-X16)/J16*100)</f>
+        <f>IF($K16="","",(U16-AB16)/J16*100)</f>
       </c>
       <c r="W16" s="3">
         <f>IF($K16="","",M16-T16)</f>
       </c>
-      <c r="Y16" s="3">
-        <f>IF($K16="","",U16-X16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC16" s="3">
+        <f>IF($K16="","",U16-AB16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="J17" s="3"/>
@@ -1472,16 +1496,16 @@
         <f>IF($K17="","",L17-M17-N17-Q17-R17-S17)</f>
       </c>
       <c r="V17" s="3">
-        <f>IF($K17="","",(U17-X17)/J17*100)</f>
+        <f>IF($K17="","",(U17-AB17)/J17*100)</f>
       </c>
       <c r="W17" s="3">
         <f>IF($K17="","",M17-T17)</f>
       </c>
-      <c r="Y17" s="3">
-        <f>IF($K17="","",U17-X17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC17" s="3">
+        <f>IF($K17="","",U17-AB17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="J18" s="3"/>
@@ -1515,16 +1539,16 @@
         <f>IF($K18="","",L18-M18-N18-Q18-R18-S18)</f>
       </c>
       <c r="V18" s="3">
-        <f>IF($K18="","",(U18-X18)/J18*100)</f>
+        <f>IF($K18="","",(U18-AB18)/J18*100)</f>
       </c>
       <c r="W18" s="3">
         <f>IF($K18="","",M18-T18)</f>
       </c>
-      <c r="Y18" s="3">
-        <f>IF($K18="","",U18-X18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC18" s="3">
+        <f>IF($K18="","",U18-AB18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="J19" s="3"/>
@@ -1558,16 +1582,16 @@
         <f>IF($K19="","",L19-M19-N19-Q19-R19-S19)</f>
       </c>
       <c r="V19" s="3">
-        <f>IF($K19="","",(U19-X19)/J19*100)</f>
+        <f>IF($K19="","",(U19-AB19)/J19*100)</f>
       </c>
       <c r="W19" s="3">
         <f>IF($K19="","",M19-T19)</f>
       </c>
-      <c r="Y19" s="3">
-        <f>IF($K19="","",U19-X19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC19" s="3">
+        <f>IF($K19="","",U19-AB19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="J20" s="3"/>
@@ -1601,16 +1625,16 @@
         <f>IF($K20="","",L20-M20-N20-Q20-R20-S20)</f>
       </c>
       <c r="V20" s="3">
-        <f>IF($K20="","",(U20-X20)/J20*100)</f>
+        <f>IF($K20="","",(U20-AB20)/J20*100)</f>
       </c>
       <c r="W20" s="3">
         <f>IF($K20="","",M20-T20)</f>
       </c>
-      <c r="Y20" s="3">
-        <f>IF($K20="","",U20-X20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC20" s="3">
+        <f>IF($K20="","",U20-AB20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="J21" s="3"/>
@@ -1644,16 +1668,16 @@
         <f>IF($K21="","",L21-M21-N21-Q21-R21-S21)</f>
       </c>
       <c r="V21" s="3">
-        <f>IF($K21="","",(U21-X21)/J21*100)</f>
+        <f>IF($K21="","",(U21-AB21)/J21*100)</f>
       </c>
       <c r="W21" s="3">
         <f>IF($K21="","",M21-T21)</f>
       </c>
-      <c r="Y21" s="3">
-        <f>IF($K21="","",U21-X21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC21" s="3">
+        <f>IF($K21="","",U21-AB21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="J22" s="3"/>
@@ -1687,16 +1711,16 @@
         <f>IF($K22="","",L22-M22-N22-Q22-R22-S22)</f>
       </c>
       <c r="V22" s="3">
-        <f>IF($K22="","",(U22-X22)/J22*100)</f>
+        <f>IF($K22="","",(U22-AB22)/J22*100)</f>
       </c>
       <c r="W22" s="3">
         <f>IF($K22="","",M22-T22)</f>
       </c>
-      <c r="Y22" s="3">
-        <f>IF($K22="","",U22-X22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC22" s="3">
+        <f>IF($K22="","",U22-AB22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="J23" s="3"/>
@@ -1730,16 +1754,16 @@
         <f>IF($K23="","",L23-M23-N23-Q23-R23-S23)</f>
       </c>
       <c r="V23" s="3">
-        <f>IF($K23="","",(U23-X23)/J23*100)</f>
+        <f>IF($K23="","",(U23-AB23)/J23*100)</f>
       </c>
       <c r="W23" s="3">
         <f>IF($K23="","",M23-T23)</f>
       </c>
-      <c r="Y23" s="3">
-        <f>IF($K23="","",U23-X23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC23" s="3">
+        <f>IF($K23="","",U23-AB23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="J24" s="3"/>
@@ -1773,16 +1797,16 @@
         <f>IF($K24="","",L24-M24-N24-Q24-R24-S24)</f>
       </c>
       <c r="V24" s="3">
-        <f>IF($K24="","",(U24-X24)/J24*100)</f>
+        <f>IF($K24="","",(U24-AB24)/J24*100)</f>
       </c>
       <c r="W24" s="3">
         <f>IF($K24="","",M24-T24)</f>
       </c>
-      <c r="Y24" s="3">
-        <f>IF($K24="","",U24-X24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC24" s="3">
+        <f>IF($K24="","",U24-AB24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="J25" s="3"/>
@@ -1816,16 +1840,16 @@
         <f>IF($K25="","",L25-M25-N25-Q25-R25-S25)</f>
       </c>
       <c r="V25" s="3">
-        <f>IF($K25="","",(U25-X25)/J25*100)</f>
+        <f>IF($K25="","",(U25-AB25)/J25*100)</f>
       </c>
       <c r="W25" s="3">
         <f>IF($K25="","",M25-T25)</f>
       </c>
-      <c r="Y25" s="3">
-        <f>IF($K25="","",U25-X25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC25" s="3">
+        <f>IF($K25="","",U25-AB25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="J26" s="3"/>
@@ -1859,16 +1883,16 @@
         <f>IF($K26="","",L26-M26-N26-Q26-R26-S26)</f>
       </c>
       <c r="V26" s="3">
-        <f>IF($K26="","",(U26-X26)/J26*100)</f>
+        <f>IF($K26="","",(U26-AB26)/J26*100)</f>
       </c>
       <c r="W26" s="3">
         <f>IF($K26="","",M26-T26)</f>
       </c>
-      <c r="Y26" s="3">
-        <f>IF($K26="","",U26-X26)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC26" s="3">
+        <f>IF($K26="","",U26-AB26)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="J27" s="3"/>
@@ -1902,16 +1926,16 @@
         <f>IF($K27="","",L27-M27-N27-Q27-R27-S27)</f>
       </c>
       <c r="V27" s="3">
-        <f>IF($K27="","",(U27-X27)/J27*100)</f>
+        <f>IF($K27="","",(U27-AB27)/J27*100)</f>
       </c>
       <c r="W27" s="3">
         <f>IF($K27="","",M27-T27)</f>
       </c>
-      <c r="Y27" s="3">
-        <f>IF($K27="","",U27-X27)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC27" s="3">
+        <f>IF($K27="","",U27-AB27)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="J28" s="3"/>
@@ -1945,16 +1969,16 @@
         <f>IF($K28="","",L28-M28-N28-Q28-R28-S28)</f>
       </c>
       <c r="V28" s="3">
-        <f>IF($K28="","",(U28-X28)/J28*100)</f>
+        <f>IF($K28="","",(U28-AB28)/J28*100)</f>
       </c>
       <c r="W28" s="3">
         <f>IF($K28="","",M28-T28)</f>
       </c>
-      <c r="Y28" s="3">
-        <f>IF($K28="","",U28-X28)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC28" s="3">
+        <f>IF($K28="","",U28-AB28)</f>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="J29" s="3"/>
@@ -1988,16 +2012,16 @@
         <f>IF($K29="","",L29-M29-N29-Q29-R29-S29)</f>
       </c>
       <c r="V29" s="3">
-        <f>IF($K29="","",(U29-X29)/J29*100)</f>
+        <f>IF($K29="","",(U29-AB29)/J29*100)</f>
       </c>
       <c r="W29" s="3">
         <f>IF($K29="","",M29-T29)</f>
       </c>
-      <c r="Y29" s="3">
-        <f>IF($K29="","",U29-X29)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC29" s="3">
+        <f>IF($K29="","",U29-AB29)</f>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="J30" s="3"/>
@@ -2031,16 +2055,16 @@
         <f>IF($K30="","",L30-M30-N30-Q30-R30-S30)</f>
       </c>
       <c r="V30" s="3">
-        <f>IF($K30="","",(U30-X30)/J30*100)</f>
+        <f>IF($K30="","",(U30-AB30)/J30*100)</f>
       </c>
       <c r="W30" s="3">
         <f>IF($K30="","",M30-T30)</f>
       </c>
-      <c r="Y30" s="3">
-        <f>IF($K30="","",U30-X30)</f>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC30" s="3">
+        <f>IF($K30="","",U30-AB30)</f>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="J31" s="3"/>
@@ -2074,16 +2098,16 @@
         <f>IF($K31="","",L31-M31-N31-Q31-R31-S31)</f>
       </c>
       <c r="V31" s="3">
-        <f>IF($K31="","",(U31-X31)/J31*100)</f>
+        <f>IF($K31="","",(U31-AB31)/J31*100)</f>
       </c>
       <c r="W31" s="3">
         <f>IF($K31="","",M31-T31)</f>
       </c>
-      <c r="Y31" s="3">
-        <f>IF($K31="","",U31-X31)</f>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC31" s="3">
+        <f>IF($K31="","",U31-AB31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="J32" s="3"/>
@@ -2117,16 +2141,16 @@
         <f>IF($K32="","",L32-M32-N32-Q32-R32-S32)</f>
       </c>
       <c r="V32" s="3">
-        <f>IF($K32="","",(U32-X32)/J32*100)</f>
+        <f>IF($K32="","",(U32-AB32)/J32*100)</f>
       </c>
       <c r="W32" s="3">
         <f>IF($K32="","",M32-T32)</f>
       </c>
-      <c r="Y32" s="3">
-        <f>IF($K32="","",U32-X32)</f>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC32" s="3">
+        <f>IF($K32="","",U32-AB32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="J33" s="3"/>
@@ -2160,16 +2184,16 @@
         <f>IF($K33="","",L33-M33-N33-Q33-R33-S33)</f>
       </c>
       <c r="V33" s="3">
-        <f>IF($K33="","",(U33-X33)/J33*100)</f>
+        <f>IF($K33="","",(U33-AB33)/J33*100)</f>
       </c>
       <c r="W33" s="3">
         <f>IF($K33="","",M33-T33)</f>
       </c>
-      <c r="Y33" s="3">
-        <f>IF($K33="","",U33-X33)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC33" s="3">
+        <f>IF($K33="","",U33-AB33)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="J34" s="3"/>
@@ -2203,16 +2227,16 @@
         <f>IF($K34="","",L34-M34-N34-Q34-R34-S34)</f>
       </c>
       <c r="V34" s="3">
-        <f>IF($K34="","",(U34-X34)/J34*100)</f>
+        <f>IF($K34="","",(U34-AB34)/J34*100)</f>
       </c>
       <c r="W34" s="3">
         <f>IF($K34="","",M34-T34)</f>
       </c>
-      <c r="Y34" s="3">
-        <f>IF($K34="","",U34-X34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC34" s="3">
+        <f>IF($K34="","",U34-AB34)</f>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="J35" s="3"/>
@@ -2246,16 +2270,16 @@
         <f>IF($K35="","",L35-M35-N35-Q35-R35-S35)</f>
       </c>
       <c r="V35" s="3">
-        <f>IF($K35="","",(U35-X35)/J35*100)</f>
+        <f>IF($K35="","",(U35-AB35)/J35*100)</f>
       </c>
       <c r="W35" s="3">
         <f>IF($K35="","",M35-T35)</f>
       </c>
-      <c r="Y35" s="3">
-        <f>IF($K35="","",U35-X35)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC35" s="3">
+        <f>IF($K35="","",U35-AB35)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="J36" s="3"/>
@@ -2289,16 +2313,16 @@
         <f>IF($K36="","",L36-M36-N36-Q36-R36-S36)</f>
       </c>
       <c r="V36" s="3">
-        <f>IF($K36="","",(U36-X36)/J36*100)</f>
+        <f>IF($K36="","",(U36-AB36)/J36*100)</f>
       </c>
       <c r="W36" s="3">
         <f>IF($K36="","",M36-T36)</f>
       </c>
-      <c r="Y36" s="3">
-        <f>IF($K36="","",U36-X36)</f>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC36" s="3">
+        <f>IF($K36="","",U36-AB36)</f>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="J37" s="3"/>
@@ -2332,16 +2356,16 @@
         <f>IF($K37="","",L37-M37-N37-Q37-R37-S37)</f>
       </c>
       <c r="V37" s="3">
-        <f>IF($K37="","",(U37-X37)/J37*100)</f>
+        <f>IF($K37="","",(U37-AB37)/J37*100)</f>
       </c>
       <c r="W37" s="3">
         <f>IF($K37="","",M37-T37)</f>
       </c>
-      <c r="Y37" s="3">
-        <f>IF($K37="","",U37-X37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC37" s="3">
+        <f>IF($K37="","",U37-AB37)</f>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="J38" s="3"/>
@@ -2375,16 +2399,16 @@
         <f>IF($K38="","",L38-M38-N38-Q38-R38-S38)</f>
       </c>
       <c r="V38" s="3">
-        <f>IF($K38="","",(U38-X38)/J38*100)</f>
+        <f>IF($K38="","",(U38-AB38)/J38*100)</f>
       </c>
       <c r="W38" s="3">
         <f>IF($K38="","",M38-T38)</f>
       </c>
-      <c r="Y38" s="3">
-        <f>IF($K38="","",U38-X38)</f>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC38" s="3">
+        <f>IF($K38="","",U38-AB38)</f>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="J39" s="3"/>
@@ -2418,16 +2442,16 @@
         <f>IF($K39="","",L39-M39-N39-Q39-R39-S39)</f>
       </c>
       <c r="V39" s="3">
-        <f>IF($K39="","",(U39-X39)/J39*100)</f>
+        <f>IF($K39="","",(U39-AB39)/J39*100)</f>
       </c>
       <c r="W39" s="3">
         <f>IF($K39="","",M39-T39)</f>
       </c>
-      <c r="Y39" s="3">
-        <f>IF($K39="","",U39-X39)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC39" s="3">
+        <f>IF($K39="","",U39-AB39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="J40" s="3"/>
@@ -2461,16 +2485,16 @@
         <f>IF($K40="","",L40-M40-N40-Q40-R40-S40)</f>
       </c>
       <c r="V40" s="3">
-        <f>IF($K40="","",(U40-X40)/J40*100)</f>
+        <f>IF($K40="","",(U40-AB40)/J40*100)</f>
       </c>
       <c r="W40" s="3">
         <f>IF($K40="","",M40-T40)</f>
       </c>
-      <c r="Y40" s="3">
-        <f>IF($K40="","",U40-X40)</f>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC40" s="3">
+        <f>IF($K40="","",U40-AB40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="J41" s="3"/>
@@ -2504,16 +2528,16 @@
         <f>IF($K41="","",L41-M41-N41-Q41-R41-S41)</f>
       </c>
       <c r="V41" s="3">
-        <f>IF($K41="","",(U41-X41)/J41*100)</f>
+        <f>IF($K41="","",(U41-AB41)/J41*100)</f>
       </c>
       <c r="W41" s="3">
         <f>IF($K41="","",M41-T41)</f>
       </c>
-      <c r="Y41" s="3">
-        <f>IF($K41="","",U41-X41)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC41" s="3">
+        <f>IF($K41="","",U41-AB41)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="J42" s="3"/>
@@ -2547,16 +2571,16 @@
         <f>IF($K42="","",L42-M42-N42-Q42-R42-S42)</f>
       </c>
       <c r="V42" s="3">
-        <f>IF($K42="","",(U42-X42)/J42*100)</f>
+        <f>IF($K42="","",(U42-AB42)/J42*100)</f>
       </c>
       <c r="W42" s="3">
         <f>IF($K42="","",M42-T42)</f>
       </c>
-      <c r="Y42" s="3">
-        <f>IF($K42="","",U42-X42)</f>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC42" s="3">
+        <f>IF($K42="","",U42-AB42)</f>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="J43" s="3"/>
@@ -2590,16 +2614,16 @@
         <f>IF($K43="","",L43-M43-N43-Q43-R43-S43)</f>
       </c>
       <c r="V43" s="3">
-        <f>IF($K43="","",(U43-X43)/J43*100)</f>
+        <f>IF($K43="","",(U43-AB43)/J43*100)</f>
       </c>
       <c r="W43" s="3">
         <f>IF($K43="","",M43-T43)</f>
       </c>
-      <c r="Y43" s="3">
-        <f>IF($K43="","",U43-X43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC43" s="3">
+        <f>IF($K43="","",U43-AB43)</f>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="J44" s="3"/>
@@ -2633,16 +2657,16 @@
         <f>IF($K44="","",L44-M44-N44-Q44-R44-S44)</f>
       </c>
       <c r="V44" s="3">
-        <f>IF($K44="","",(U44-X44)/J44*100)</f>
+        <f>IF($K44="","",(U44-AB44)/J44*100)</f>
       </c>
       <c r="W44" s="3">
         <f>IF($K44="","",M44-T44)</f>
       </c>
-      <c r="Y44" s="3">
-        <f>IF($K44="","",U44-X44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC44" s="3">
+        <f>IF($K44="","",U44-AB44)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="J45" s="3"/>
@@ -2676,16 +2700,16 @@
         <f>IF($K45="","",L45-M45-N45-Q45-R45-S45)</f>
       </c>
       <c r="V45" s="3">
-        <f>IF($K45="","",(U45-X45)/J45*100)</f>
+        <f>IF($K45="","",(U45-AB45)/J45*100)</f>
       </c>
       <c r="W45" s="3">
         <f>IF($K45="","",M45-T45)</f>
       </c>
-      <c r="Y45" s="3">
-        <f>IF($K45="","",U45-X45)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC45" s="3">
+        <f>IF($K45="","",U45-AB45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="J46" s="3"/>
@@ -2719,16 +2743,16 @@
         <f>IF($K46="","",L46-M46-N46-Q46-R46-S46)</f>
       </c>
       <c r="V46" s="3">
-        <f>IF($K46="","",(U46-X46)/J46*100)</f>
+        <f>IF($K46="","",(U46-AB46)/J46*100)</f>
       </c>
       <c r="W46" s="3">
         <f>IF($K46="","",M46-T46)</f>
       </c>
-      <c r="Y46" s="3">
-        <f>IF($K46="","",U46-X46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC46" s="3">
+        <f>IF($K46="","",U46-AB46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="J47" s="3"/>
@@ -2762,16 +2786,16 @@
         <f>IF($K47="","",L47-M47-N47-Q47-R47-S47)</f>
       </c>
       <c r="V47" s="3">
-        <f>IF($K47="","",(U47-X47)/J47*100)</f>
+        <f>IF($K47="","",(U47-AB47)/J47*100)</f>
       </c>
       <c r="W47" s="3">
         <f>IF($K47="","",M47-T47)</f>
       </c>
-      <c r="Y47" s="3">
-        <f>IF($K47="","",U47-X47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC47" s="3">
+        <f>IF($K47="","",U47-AB47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="J48" s="3"/>
@@ -2805,16 +2829,16 @@
         <f>IF($K48="","",L48-M48-N48-Q48-R48-S48)</f>
       </c>
       <c r="V48" s="3">
-        <f>IF($K48="","",(U48-X48)/J48*100)</f>
+        <f>IF($K48="","",(U48-AB48)/J48*100)</f>
       </c>
       <c r="W48" s="3">
         <f>IF($K48="","",M48-T48)</f>
       </c>
-      <c r="Y48" s="3">
-        <f>IF($K48="","",U48-X48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC48" s="3">
+        <f>IF($K48="","",U48-AB48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="J49" s="3"/>
@@ -2848,16 +2872,16 @@
         <f>IF($K49="","",L49-M49-N49-Q49-R49-S49)</f>
       </c>
       <c r="V49" s="3">
-        <f>IF($K49="","",(U49-X49)/J49*100)</f>
+        <f>IF($K49="","",(U49-AB49)/J49*100)</f>
       </c>
       <c r="W49" s="3">
         <f>IF($K49="","",M49-T49)</f>
       </c>
-      <c r="Y49" s="3">
-        <f>IF($K49="","",U49-X49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC49" s="3">
+        <f>IF($K49="","",U49-AB49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="J50" s="3"/>
@@ -2891,16 +2915,16 @@
         <f>IF($K50="","",L50-M50-N50-Q50-R50-S50)</f>
       </c>
       <c r="V50" s="3">
-        <f>IF($K50="","",(U50-X50)/J50*100)</f>
+        <f>IF($K50="","",(U50-AB50)/J50*100)</f>
       </c>
       <c r="W50" s="3">
         <f>IF($K50="","",M50-T50)</f>
       </c>
-      <c r="Y50" s="3">
-        <f>IF($K50="","",U50-X50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC50" s="3">
+        <f>IF($K50="","",U50-AB50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="J51" s="3"/>
@@ -2934,16 +2958,16 @@
         <f>IF($K51="","",L51-M51-N51-Q51-R51-S51)</f>
       </c>
       <c r="V51" s="3">
-        <f>IF($K51="","",(U51-X51)/J51*100)</f>
+        <f>IF($K51="","",(U51-AB51)/J51*100)</f>
       </c>
       <c r="W51" s="3">
         <f>IF($K51="","",M51-T51)</f>
       </c>
-      <c r="Y51" s="3">
-        <f>IF($K51="","",U51-X51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC51" s="3">
+        <f>IF($K51="","",U51-AB51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="J52" s="3"/>
@@ -2977,16 +3001,16 @@
         <f>IF($K52="","",L52-M52-N52-Q52-R52-S52)</f>
       </c>
       <c r="V52" s="3">
-        <f>IF($K52="","",(U52-X52)/J52*100)</f>
+        <f>IF($K52="","",(U52-AB52)/J52*100)</f>
       </c>
       <c r="W52" s="3">
         <f>IF($K52="","",M52-T52)</f>
       </c>
-      <c r="Y52" s="3">
-        <f>IF($K52="","",U52-X52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC52" s="3">
+        <f>IF($K52="","",U52-AB52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="J53" s="3"/>
@@ -3020,16 +3044,16 @@
         <f>IF($K53="","",L53-M53-N53-Q53-R53-S53)</f>
       </c>
       <c r="V53" s="3">
-        <f>IF($K53="","",(U53-X53)/J53*100)</f>
+        <f>IF($K53="","",(U53-AB53)/J53*100)</f>
       </c>
       <c r="W53" s="3">
         <f>IF($K53="","",M53-T53)</f>
       </c>
-      <c r="Y53" s="3">
-        <f>IF($K53="","",U53-X53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC53" s="3">
+        <f>IF($K53="","",U53-AB53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="J54" s="3"/>
@@ -3063,16 +3087,16 @@
         <f>IF($K54="","",L54-M54-N54-Q54-R54-S54)</f>
       </c>
       <c r="V54" s="3">
-        <f>IF($K54="","",(U54-X54)/J54*100)</f>
+        <f>IF($K54="","",(U54-AB54)/J54*100)</f>
       </c>
       <c r="W54" s="3">
         <f>IF($K54="","",M54-T54)</f>
       </c>
-      <c r="Y54" s="3">
-        <f>IF($K54="","",U54-X54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC54" s="3">
+        <f>IF($K54="","",U54-AB54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="J55" s="3"/>
@@ -3106,16 +3130,16 @@
         <f>IF($K55="","",L55-M55-N55-Q55-R55-S55)</f>
       </c>
       <c r="V55" s="3">
-        <f>IF($K55="","",(U55-X55)/J55*100)</f>
+        <f>IF($K55="","",(U55-AB55)/J55*100)</f>
       </c>
       <c r="W55" s="3">
         <f>IF($K55="","",M55-T55)</f>
       </c>
-      <c r="Y55" s="3">
-        <f>IF($K55="","",U55-X55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC55" s="3">
+        <f>IF($K55="","",U55-AB55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="J56" s="3"/>
@@ -3149,16 +3173,16 @@
         <f>IF($K56="","",L56-M56-N56-Q56-R56-S56)</f>
       </c>
       <c r="V56" s="3">
-        <f>IF($K56="","",(U56-X56)/J56*100)</f>
+        <f>IF($K56="","",(U56-AB56)/J56*100)</f>
       </c>
       <c r="W56" s="3">
         <f>IF($K56="","",M56-T56)</f>
       </c>
-      <c r="Y56" s="3">
-        <f>IF($K56="","",U56-X56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC56" s="3">
+        <f>IF($K56="","",U56-AB56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="J57" s="3"/>
@@ -3192,16 +3216,16 @@
         <f>IF($K57="","",L57-M57-N57-Q57-R57-S57)</f>
       </c>
       <c r="V57" s="3">
-        <f>IF($K57="","",(U57-X57)/J57*100)</f>
+        <f>IF($K57="","",(U57-AB57)/J57*100)</f>
       </c>
       <c r="W57" s="3">
         <f>IF($K57="","",M57-T57)</f>
       </c>
-      <c r="Y57" s="3">
-        <f>IF($K57="","",U57-X57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC57" s="3">
+        <f>IF($K57="","",U57-AB57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="J58" s="3"/>
@@ -3235,16 +3259,16 @@
         <f>IF($K58="","",L58-M58-N58-Q58-R58-S58)</f>
       </c>
       <c r="V58" s="3">
-        <f>IF($K58="","",(U58-X58)/J58*100)</f>
+        <f>IF($K58="","",(U58-AB58)/J58*100)</f>
       </c>
       <c r="W58" s="3">
         <f>IF($K58="","",M58-T58)</f>
       </c>
-      <c r="Y58" s="3">
-        <f>IF($K58="","",U58-X58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC58" s="3">
+        <f>IF($K58="","",U58-AB58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="J59" s="3"/>
@@ -3278,16 +3302,16 @@
         <f>IF($K59="","",L59-M59-N59-Q59-R59-S59)</f>
       </c>
       <c r="V59" s="3">
-        <f>IF($K59="","",(U59-X59)/J59*100)</f>
+        <f>IF($K59="","",(U59-AB59)/J59*100)</f>
       </c>
       <c r="W59" s="3">
         <f>IF($K59="","",M59-T59)</f>
       </c>
-      <c r="Y59" s="3">
-        <f>IF($K59="","",U59-X59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC59" s="3">
+        <f>IF($K59="","",U59-AB59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="J60" s="3"/>
@@ -3321,16 +3345,16 @@
         <f>IF($K60="","",L60-M60-N60-Q60-R60-S60)</f>
       </c>
       <c r="V60" s="3">
-        <f>IF($K60="","",(U60-X60)/J60*100)</f>
+        <f>IF($K60="","",(U60-AB60)/J60*100)</f>
       </c>
       <c r="W60" s="3">
         <f>IF($K60="","",M60-T60)</f>
       </c>
-      <c r="Y60" s="3">
-        <f>IF($K60="","",U60-X60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC60" s="3">
+        <f>IF($K60="","",U60-AB60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="J61" s="3"/>
@@ -3364,16 +3388,16 @@
         <f>IF($K61="","",L61-M61-N61-Q61-R61-S61)</f>
       </c>
       <c r="V61" s="3">
-        <f>IF($K61="","",(U61-X61)/J61*100)</f>
+        <f>IF($K61="","",(U61-AB61)/J61*100)</f>
       </c>
       <c r="W61" s="3">
         <f>IF($K61="","",M61-T61)</f>
       </c>
-      <c r="Y61" s="3">
-        <f>IF($K61="","",U61-X61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC61" s="3">
+        <f>IF($K61="","",U61-AB61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="J62" s="3"/>
@@ -3407,16 +3431,16 @@
         <f>IF($K62="","",L62-M62-N62-Q62-R62-S62)</f>
       </c>
       <c r="V62" s="3">
-        <f>IF($K62="","",(U62-X62)/J62*100)</f>
+        <f>IF($K62="","",(U62-AB62)/J62*100)</f>
       </c>
       <c r="W62" s="3">
         <f>IF($K62="","",M62-T62)</f>
       </c>
-      <c r="Y62" s="3">
-        <f>IF($K62="","",U62-X62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC62" s="3">
+        <f>IF($K62="","",U62-AB62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="J63" s="3"/>
@@ -3450,16 +3474,16 @@
         <f>IF($K63="","",L63-M63-N63-Q63-R63-S63)</f>
       </c>
       <c r="V63" s="3">
-        <f>IF($K63="","",(U63-X63)/J63*100)</f>
+        <f>IF($K63="","",(U63-AB63)/J63*100)</f>
       </c>
       <c r="W63" s="3">
         <f>IF($K63="","",M63-T63)</f>
       </c>
-      <c r="Y63" s="3">
-        <f>IF($K63="","",U63-X63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC63" s="3">
+        <f>IF($K63="","",U63-AB63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="J64" s="3"/>
@@ -3493,16 +3517,16 @@
         <f>IF($K64="","",L64-M64-N64-Q64-R64-S64)</f>
       </c>
       <c r="V64" s="3">
-        <f>IF($K64="","",(U64-X64)/J64*100)</f>
+        <f>IF($K64="","",(U64-AB64)/J64*100)</f>
       </c>
       <c r="W64" s="3">
         <f>IF($K64="","",M64-T64)</f>
       </c>
-      <c r="Y64" s="3">
-        <f>IF($K64="","",U64-X64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC64" s="3">
+        <f>IF($K64="","",U64-AB64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="J65" s="3"/>
@@ -3536,16 +3560,16 @@
         <f>IF($K65="","",L65-M65-N65-Q65-R65-S65)</f>
       </c>
       <c r="V65" s="3">
-        <f>IF($K65="","",(U65-X65)/J65*100)</f>
+        <f>IF($K65="","",(U65-AB65)/J65*100)</f>
       </c>
       <c r="W65" s="3">
         <f>IF($K65="","",M65-T65)</f>
       </c>
-      <c r="Y65" s="3">
-        <f>IF($K65="","",U65-X65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC65" s="3">
+        <f>IF($K65="","",U65-AB65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="J66" s="3"/>
@@ -3579,16 +3603,16 @@
         <f>IF($K66="","",L66-M66-N66-Q66-R66-S66)</f>
       </c>
       <c r="V66" s="3">
-        <f>IF($K66="","",(U66-X66)/J66*100)</f>
+        <f>IF($K66="","",(U66-AB66)/J66*100)</f>
       </c>
       <c r="W66" s="3">
         <f>IF($K66="","",M66-T66)</f>
       </c>
-      <c r="Y66" s="3">
-        <f>IF($K66="","",U66-X66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC66" s="3">
+        <f>IF($K66="","",U66-AB66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="J67" s="3"/>
@@ -3622,16 +3646,16 @@
         <f>IF($K67="","",L67-M67-N67-Q67-R67-S67)</f>
       </c>
       <c r="V67" s="3">
-        <f>IF($K67="","",(U67-X67)/J67*100)</f>
+        <f>IF($K67="","",(U67-AB67)/J67*100)</f>
       </c>
       <c r="W67" s="3">
         <f>IF($K67="","",M67-T67)</f>
       </c>
-      <c r="Y67" s="3">
-        <f>IF($K67="","",U67-X67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC67" s="3">
+        <f>IF($K67="","",U67-AB67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="J68" s="3"/>
@@ -3665,16 +3689,16 @@
         <f>IF($K68="","",L68-M68-N68-Q68-R68-S68)</f>
       </c>
       <c r="V68" s="3">
-        <f>IF($K68="","",(U68-X68)/J68*100)</f>
+        <f>IF($K68="","",(U68-AB68)/J68*100)</f>
       </c>
       <c r="W68" s="3">
         <f>IF($K68="","",M68-T68)</f>
       </c>
-      <c r="Y68" s="3">
-        <f>IF($K68="","",U68-X68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC68" s="3">
+        <f>IF($K68="","",U68-AB68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="J69" s="3"/>
@@ -3708,16 +3732,16 @@
         <f>IF($K69="","",L69-M69-N69-Q69-R69-S69)</f>
       </c>
       <c r="V69" s="3">
-        <f>IF($K69="","",(U69-X69)/J69*100)</f>
+        <f>IF($K69="","",(U69-AB69)/J69*100)</f>
       </c>
       <c r="W69" s="3">
         <f>IF($K69="","",M69-T69)</f>
       </c>
-      <c r="Y69" s="3">
-        <f>IF($K69="","",U69-X69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC69" s="3">
+        <f>IF($K69="","",U69-AB69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="J70" s="3"/>
@@ -3751,16 +3775,16 @@
         <f>IF($K70="","",L70-M70-N70-Q70-R70-S70)</f>
       </c>
       <c r="V70" s="3">
-        <f>IF($K70="","",(U70-X70)/J70*100)</f>
+        <f>IF($K70="","",(U70-AB70)/J70*100)</f>
       </c>
       <c r="W70" s="3">
         <f>IF($K70="","",M70-T70)</f>
       </c>
-      <c r="Y70" s="3">
-        <f>IF($K70="","",U70-X70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC70" s="3">
+        <f>IF($K70="","",U70-AB70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="J71" s="3"/>
@@ -3794,16 +3818,16 @@
         <f>IF($K71="","",L71-M71-N71-Q71-R71-S71)</f>
       </c>
       <c r="V71" s="3">
-        <f>IF($K71="","",(U71-X71)/J71*100)</f>
+        <f>IF($K71="","",(U71-AB71)/J71*100)</f>
       </c>
       <c r="W71" s="3">
         <f>IF($K71="","",M71-T71)</f>
       </c>
-      <c r="Y71" s="3">
-        <f>IF($K71="","",U71-X71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC71" s="3">
+        <f>IF($K71="","",U71-AB71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="J72" s="3"/>
@@ -3837,16 +3861,16 @@
         <f>IF($K72="","",L72-M72-N72-Q72-R72-S72)</f>
       </c>
       <c r="V72" s="3">
-        <f>IF($K72="","",(U72-X72)/J72*100)</f>
+        <f>IF($K72="","",(U72-AB72)/J72*100)</f>
       </c>
       <c r="W72" s="3">
         <f>IF($K72="","",M72-T72)</f>
       </c>
-      <c r="Y72" s="3">
-        <f>IF($K72="","",U72-X72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC72" s="3">
+        <f>IF($K72="","",U72-AB72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="J73" s="3"/>
@@ -3880,16 +3904,16 @@
         <f>IF($K73="","",L73-M73-N73-Q73-R73-S73)</f>
       </c>
       <c r="V73" s="3">
-        <f>IF($K73="","",(U73-X73)/J73*100)</f>
+        <f>IF($K73="","",(U73-AB73)/J73*100)</f>
       </c>
       <c r="W73" s="3">
         <f>IF($K73="","",M73-T73)</f>
       </c>
-      <c r="Y73" s="3">
-        <f>IF($K73="","",U73-X73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC73" s="3">
+        <f>IF($K73="","",U73-AB73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="J74" s="3"/>
@@ -3923,16 +3947,16 @@
         <f>IF($K74="","",L74-M74-N74-Q74-R74-S74)</f>
       </c>
       <c r="V74" s="3">
-        <f>IF($K74="","",(U74-X74)/J74*100)</f>
+        <f>IF($K74="","",(U74-AB74)/J74*100)</f>
       </c>
       <c r="W74" s="3">
         <f>IF($K74="","",M74-T74)</f>
       </c>
-      <c r="Y74" s="3">
-        <f>IF($K74="","",U74-X74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC74" s="3">
+        <f>IF($K74="","",U74-AB74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="J75" s="3"/>
@@ -3966,16 +3990,16 @@
         <f>IF($K75="","",L75-M75-N75-Q75-R75-S75)</f>
       </c>
       <c r="V75" s="3">
-        <f>IF($K75="","",(U75-X75)/J75*100)</f>
+        <f>IF($K75="","",(U75-AB75)/J75*100)</f>
       </c>
       <c r="W75" s="3">
         <f>IF($K75="","",M75-T75)</f>
       </c>
-      <c r="Y75" s="3">
-        <f>IF($K75="","",U75-X75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC75" s="3">
+        <f>IF($K75="","",U75-AB75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="J76" s="3"/>
@@ -4009,16 +4033,16 @@
         <f>IF($K76="","",L76-M76-N76-Q76-R76-S76)</f>
       </c>
       <c r="V76" s="3">
-        <f>IF($K76="","",(U76-X76)/J76*100)</f>
+        <f>IF($K76="","",(U76-AB76)/J76*100)</f>
       </c>
       <c r="W76" s="3">
         <f>IF($K76="","",M76-T76)</f>
       </c>
-      <c r="Y76" s="3">
-        <f>IF($K76="","",U76-X76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC76" s="3">
+        <f>IF($K76="","",U76-AB76)</f>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="J77" s="3"/>
@@ -4052,16 +4076,16 @@
         <f>IF($K77="","",L77-M77-N77-Q77-R77-S77)</f>
       </c>
       <c r="V77" s="3">
-        <f>IF($K77="","",(U77-X77)/J77*100)</f>
+        <f>IF($K77="","",(U77-AB77)/J77*100)</f>
       </c>
       <c r="W77" s="3">
         <f>IF($K77="","",M77-T77)</f>
       </c>
-      <c r="Y77" s="3">
-        <f>IF($K77="","",U77-X77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC77" s="3">
+        <f>IF($K77="","",U77-AB77)</f>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="J78" s="3"/>
@@ -4095,16 +4119,16 @@
         <f>IF($K78="","",L78-M78-N78-Q78-R78-S78)</f>
       </c>
       <c r="V78" s="3">
-        <f>IF($K78="","",(U78-X78)/J78*100)</f>
+        <f>IF($K78="","",(U78-AB78)/J78*100)</f>
       </c>
       <c r="W78" s="3">
         <f>IF($K78="","",M78-T78)</f>
       </c>
-      <c r="Y78" s="3">
-        <f>IF($K78="","",U78-X78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC78" s="3">
+        <f>IF($K78="","",U78-AB78)</f>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="J79" s="3"/>
@@ -4138,16 +4162,16 @@
         <f>IF($K79="","",L79-M79-N79-Q79-R79-S79)</f>
       </c>
       <c r="V79" s="3">
-        <f>IF($K79="","",(U79-X79)/J79*100)</f>
+        <f>IF($K79="","",(U79-AB79)/J79*100)</f>
       </c>
       <c r="W79" s="3">
         <f>IF($K79="","",M79-T79)</f>
       </c>
-      <c r="Y79" s="3">
-        <f>IF($K79="","",U79-X79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC79" s="3">
+        <f>IF($K79="","",U79-AB79)</f>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="J80" s="3"/>
@@ -4181,16 +4205,16 @@
         <f>IF($K80="","",L80-M80-N80-Q80-R80-S80)</f>
       </c>
       <c r="V80" s="3">
-        <f>IF($K80="","",(U80-X80)/J80*100)</f>
+        <f>IF($K80="","",(U80-AB80)/J80*100)</f>
       </c>
       <c r="W80" s="3">
         <f>IF($K80="","",M80-T80)</f>
       </c>
-      <c r="Y80" s="3">
-        <f>IF($K80="","",U80-X80)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC80" s="3">
+        <f>IF($K80="","",U80-AB80)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="J81" s="3"/>
@@ -4224,16 +4248,16 @@
         <f>IF($K81="","",L81-M81-N81-Q81-R81-S81)</f>
       </c>
       <c r="V81" s="3">
-        <f>IF($K81="","",(U81-X81)/J81*100)</f>
+        <f>IF($K81="","",(U81-AB81)/J81*100)</f>
       </c>
       <c r="W81" s="3">
         <f>IF($K81="","",M81-T81)</f>
       </c>
-      <c r="Y81" s="3">
-        <f>IF($K81="","",U81-X81)</f>
-      </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC81" s="3">
+        <f>IF($K81="","",U81-AB81)</f>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="J82" s="3"/>
@@ -4267,16 +4291,16 @@
         <f>IF($K82="","",L82-M82-N82-Q82-R82-S82)</f>
       </c>
       <c r="V82" s="3">
-        <f>IF($K82="","",(U82-X82)/J82*100)</f>
+        <f>IF($K82="","",(U82-AB82)/J82*100)</f>
       </c>
       <c r="W82" s="3">
         <f>IF($K82="","",M82-T82)</f>
       </c>
-      <c r="Y82" s="3">
-        <f>IF($K82="","",U82-X82)</f>
-      </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC82" s="3">
+        <f>IF($K82="","",U82-AB82)</f>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="J83" s="3"/>
@@ -4310,16 +4334,16 @@
         <f>IF($K83="","",L83-M83-N83-Q83-R83-S83)</f>
       </c>
       <c r="V83" s="3">
-        <f>IF($K83="","",(U83-X83)/J83*100)</f>
+        <f>IF($K83="","",(U83-AB83)/J83*100)</f>
       </c>
       <c r="W83" s="3">
         <f>IF($K83="","",M83-T83)</f>
       </c>
-      <c r="Y83" s="3">
-        <f>IF($K83="","",U83-X83)</f>
-      </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC83" s="3">
+        <f>IF($K83="","",U83-AB83)</f>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="J84" s="3"/>
@@ -4353,16 +4377,16 @@
         <f>IF($K84="","",L84-M84-N84-Q84-R84-S84)</f>
       </c>
       <c r="V84" s="3">
-        <f>IF($K84="","",(U84-X84)/J84*100)</f>
+        <f>IF($K84="","",(U84-AB84)/J84*100)</f>
       </c>
       <c r="W84" s="3">
         <f>IF($K84="","",M84-T84)</f>
       </c>
-      <c r="Y84" s="3">
-        <f>IF($K84="","",U84-X84)</f>
-      </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC84" s="3">
+        <f>IF($K84="","",U84-AB84)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="J85" s="3"/>
@@ -4396,16 +4420,16 @@
         <f>IF($K85="","",L85-M85-N85-Q85-R85-S85)</f>
       </c>
       <c r="V85" s="3">
-        <f>IF($K85="","",(U85-X85)/J85*100)</f>
+        <f>IF($K85="","",(U85-AB85)/J85*100)</f>
       </c>
       <c r="W85" s="3">
         <f>IF($K85="","",M85-T85)</f>
       </c>
-      <c r="Y85" s="3">
-        <f>IF($K85="","",U85-X85)</f>
-      </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC85" s="3">
+        <f>IF($K85="","",U85-AB85)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="J86" s="3"/>
@@ -4439,16 +4463,16 @@
         <f>IF($K86="","",L86-M86-N86-Q86-R86-S86)</f>
       </c>
       <c r="V86" s="3">
-        <f>IF($K86="","",(U86-X86)/J86*100)</f>
+        <f>IF($K86="","",(U86-AB86)/J86*100)</f>
       </c>
       <c r="W86" s="3">
         <f>IF($K86="","",M86-T86)</f>
       </c>
-      <c r="Y86" s="3">
-        <f>IF($K86="","",U86-X86)</f>
-      </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC86" s="3">
+        <f>IF($K86="","",U86-AB86)</f>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="J87" s="3"/>
@@ -4482,16 +4506,16 @@
         <f>IF($K87="","",L87-M87-N87-Q87-R87-S87)</f>
       </c>
       <c r="V87" s="3">
-        <f>IF($K87="","",(U87-X87)/J87*100)</f>
+        <f>IF($K87="","",(U87-AB87)/J87*100)</f>
       </c>
       <c r="W87" s="3">
         <f>IF($K87="","",M87-T87)</f>
       </c>
-      <c r="Y87" s="3">
-        <f>IF($K87="","",U87-X87)</f>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC87" s="3">
+        <f>IF($K87="","",U87-AB87)</f>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="J88" s="3"/>
@@ -4525,16 +4549,16 @@
         <f>IF($K88="","",L88-M88-N88-Q88-R88-S88)</f>
       </c>
       <c r="V88" s="3">
-        <f>IF($K88="","",(U88-X88)/J88*100)</f>
+        <f>IF($K88="","",(U88-AB88)/J88*100)</f>
       </c>
       <c r="W88" s="3">
         <f>IF($K88="","",M88-T88)</f>
       </c>
-      <c r="Y88" s="3">
-        <f>IF($K88="","",U88-X88)</f>
-      </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC88" s="3">
+        <f>IF($K88="","",U88-AB88)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="J89" s="3"/>
@@ -4568,16 +4592,16 @@
         <f>IF($K89="","",L89-M89-N89-Q89-R89-S89)</f>
       </c>
       <c r="V89" s="3">
-        <f>IF($K89="","",(U89-X89)/J89*100)</f>
+        <f>IF($K89="","",(U89-AB89)/J89*100)</f>
       </c>
       <c r="W89" s="3">
         <f>IF($K89="","",M89-T89)</f>
       </c>
-      <c r="Y89" s="3">
-        <f>IF($K89="","",U89-X89)</f>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC89" s="3">
+        <f>IF($K89="","",U89-AB89)</f>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="J90" s="3"/>
@@ -4611,16 +4635,16 @@
         <f>IF($K90="","",L90-M90-N90-Q90-R90-S90)</f>
       </c>
       <c r="V90" s="3">
-        <f>IF($K90="","",(U90-X90)/J90*100)</f>
+        <f>IF($K90="","",(U90-AB90)/J90*100)</f>
       </c>
       <c r="W90" s="3">
         <f>IF($K90="","",M90-T90)</f>
       </c>
-      <c r="Y90" s="3">
-        <f>IF($K90="","",U90-X90)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC90" s="3">
+        <f>IF($K90="","",U90-AB90)</f>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="J91" s="3"/>
@@ -4654,16 +4678,16 @@
         <f>IF($K91="","",L91-M91-N91-Q91-R91-S91)</f>
       </c>
       <c r="V91" s="3">
-        <f>IF($K91="","",(U91-X91)/J91*100)</f>
+        <f>IF($K91="","",(U91-AB91)/J91*100)</f>
       </c>
       <c r="W91" s="3">
         <f>IF($K91="","",M91-T91)</f>
       </c>
-      <c r="Y91" s="3">
-        <f>IF($K91="","",U91-X91)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC91" s="3">
+        <f>IF($K91="","",U91-AB91)</f>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="J92" s="3"/>
@@ -4697,16 +4721,16 @@
         <f>IF($K92="","",L92-M92-N92-Q92-R92-S92)</f>
       </c>
       <c r="V92" s="3">
-        <f>IF($K92="","",(U92-X92)/J92*100)</f>
+        <f>IF($K92="","",(U92-AB92)/J92*100)</f>
       </c>
       <c r="W92" s="3">
         <f>IF($K92="","",M92-T92)</f>
       </c>
-      <c r="Y92" s="3">
-        <f>IF($K92="","",U92-X92)</f>
-      </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC92" s="3">
+        <f>IF($K92="","",U92-AB92)</f>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="J93" s="3"/>
@@ -4740,16 +4764,16 @@
         <f>IF($K93="","",L93-M93-N93-Q93-R93-S93)</f>
       </c>
       <c r="V93" s="3">
-        <f>IF($K93="","",(U93-X93)/J93*100)</f>
+        <f>IF($K93="","",(U93-AB93)/J93*100)</f>
       </c>
       <c r="W93" s="3">
         <f>IF($K93="","",M93-T93)</f>
       </c>
-      <c r="Y93" s="3">
-        <f>IF($K93="","",U93-X93)</f>
-      </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC93" s="3">
+        <f>IF($K93="","",U93-AB93)</f>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="J94" s="3"/>
@@ -4783,16 +4807,16 @@
         <f>IF($K94="","",L94-M94-N94-Q94-R94-S94)</f>
       </c>
       <c r="V94" s="3">
-        <f>IF($K94="","",(U94-X94)/J94*100)</f>
+        <f>IF($K94="","",(U94-AB94)/J94*100)</f>
       </c>
       <c r="W94" s="3">
         <f>IF($K94="","",M94-T94)</f>
       </c>
-      <c r="Y94" s="3">
-        <f>IF($K94="","",U94-X94)</f>
-      </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC94" s="3">
+        <f>IF($K94="","",U94-AB94)</f>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="J95" s="3"/>
@@ -4826,16 +4850,16 @@
         <f>IF($K95="","",L95-M95-N95-Q95-R95-S95)</f>
       </c>
       <c r="V95" s="3">
-        <f>IF($K95="","",(U95-X95)/J95*100)</f>
+        <f>IF($K95="","",(U95-AB95)/J95*100)</f>
       </c>
       <c r="W95" s="3">
         <f>IF($K95="","",M95-T95)</f>
       </c>
-      <c r="Y95" s="3">
-        <f>IF($K95="","",U95-X95)</f>
-      </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC95" s="3">
+        <f>IF($K95="","",U95-AB95)</f>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="J96" s="3"/>
@@ -4869,16 +4893,16 @@
         <f>IF($K96="","",L96-M96-N96-Q96-R96-S96)</f>
       </c>
       <c r="V96" s="3">
-        <f>IF($K96="","",(U96-X96)/J96*100)</f>
+        <f>IF($K96="","",(U96-AB96)/J96*100)</f>
       </c>
       <c r="W96" s="3">
         <f>IF($K96="","",M96-T96)</f>
       </c>
-      <c r="Y96" s="3">
-        <f>IF($K96="","",U96-X96)</f>
-      </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC96" s="3">
+        <f>IF($K96="","",U96-AB96)</f>
+      </c>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="J97" s="3"/>
@@ -4912,16 +4936,16 @@
         <f>IF($K97="","",L97-M97-N97-Q97-R97-S97)</f>
       </c>
       <c r="V97" s="3">
-        <f>IF($K97="","",(U97-X97)/J97*100)</f>
+        <f>IF($K97="","",(U97-AB97)/J97*100)</f>
       </c>
       <c r="W97" s="3">
         <f>IF($K97="","",M97-T97)</f>
       </c>
-      <c r="Y97" s="3">
-        <f>IF($K97="","",U97-X97)</f>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC97" s="3">
+        <f>IF($K97="","",U97-AB97)</f>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="J98" s="3"/>
@@ -4955,16 +4979,16 @@
         <f>IF($K98="","",L98-M98-N98-Q98-R98-S98)</f>
       </c>
       <c r="V98" s="3">
-        <f>IF($K98="","",(U98-X98)/J98*100)</f>
+        <f>IF($K98="","",(U98-AB98)/J98*100)</f>
       </c>
       <c r="W98" s="3">
         <f>IF($K98="","",M98-T98)</f>
       </c>
-      <c r="Y98" s="3">
-        <f>IF($K98="","",U98-X98)</f>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC98" s="3">
+        <f>IF($K98="","",U98-AB98)</f>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="J99" s="3"/>
@@ -4998,16 +5022,16 @@
         <f>IF($K99="","",L99-M99-N99-Q99-R99-S99)</f>
       </c>
       <c r="V99" s="3">
-        <f>IF($K99="","",(U99-X99)/J99*100)</f>
+        <f>IF($K99="","",(U99-AB99)/J99*100)</f>
       </c>
       <c r="W99" s="3">
         <f>IF($K99="","",M99-T99)</f>
       </c>
-      <c r="Y99" s="3">
-        <f>IF($K99="","",U99-X99)</f>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC99" s="3">
+        <f>IF($K99="","",U99-AB99)</f>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="J100" s="3"/>
@@ -5041,16 +5065,16 @@
         <f>IF($K100="","",L100-M100-N100-Q100-R100-S100)</f>
       </c>
       <c r="V100" s="3">
-        <f>IF($K100="","",(U100-X100)/J100*100)</f>
+        <f>IF($K100="","",(U100-AB100)/J100*100)</f>
       </c>
       <c r="W100" s="3">
         <f>IF($K100="","",M100-T100)</f>
       </c>
-      <c r="Y100" s="3">
-        <f>IF($K100="","",U100-X100)</f>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC100" s="3">
+        <f>IF($K100="","",U100-AB100)</f>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="J101" s="3"/>
@@ -5084,16 +5108,16 @@
         <f>IF($K101="","",L101-M101-N101-Q101-R101-S101)</f>
       </c>
       <c r="V101" s="3">
-        <f>IF($K101="","",(U101-X101)/J101*100)</f>
+        <f>IF($K101="","",(U101-AB101)/J101*100)</f>
       </c>
       <c r="W101" s="3">
         <f>IF($K101="","",M101-T101)</f>
       </c>
-      <c r="Y101" s="3">
-        <f>IF($K101="","",U101-X101)</f>
-      </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC101" s="3">
+        <f>IF($K101="","",U101-AB101)</f>
+      </c>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="J102" s="3"/>
@@ -5127,16 +5151,16 @@
         <f>IF($K102="","",L102-M102-N102-Q102-R102-S102)</f>
       </c>
       <c r="V102" s="3">
-        <f>IF($K102="","",(U102-X102)/J102*100)</f>
+        <f>IF($K102="","",(U102-AB102)/J102*100)</f>
       </c>
       <c r="W102" s="3">
         <f>IF($K102="","",M102-T102)</f>
       </c>
-      <c r="Y102" s="3">
-        <f>IF($K102="","",U102-X102)</f>
-      </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC102" s="3">
+        <f>IF($K102="","",U102-AB102)</f>
+      </c>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="J103" s="3"/>
@@ -5170,16 +5194,16 @@
         <f>IF($K103="","",L103-M103-N103-Q103-R103-S103)</f>
       </c>
       <c r="V103" s="3">
-        <f>IF($K103="","",(U103-X103)/J103*100)</f>
+        <f>IF($K103="","",(U103-AB103)/J103*100)</f>
       </c>
       <c r="W103" s="3">
         <f>IF($K103="","",M103-T103)</f>
       </c>
-      <c r="Y103" s="3">
-        <f>IF($K103="","",U103-X103)</f>
-      </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC103" s="3">
+        <f>IF($K103="","",U103-AB103)</f>
+      </c>
+    </row>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="J104" s="3"/>
@@ -5213,16 +5237,16 @@
         <f>IF($K104="","",L104-M104-N104-Q104-R104-S104)</f>
       </c>
       <c r="V104" s="3">
-        <f>IF($K104="","",(U104-X104)/J104*100)</f>
+        <f>IF($K104="","",(U104-AB104)/J104*100)</f>
       </c>
       <c r="W104" s="3">
         <f>IF($K104="","",M104-T104)</f>
       </c>
-      <c r="Y104" s="3">
-        <f>IF($K104="","",U104-X104)</f>
-      </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC104" s="3">
+        <f>IF($K104="","",U104-AB104)</f>
+      </c>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="J105" s="3"/>
@@ -5256,16 +5280,16 @@
         <f>IF($K105="","",L105-M105-N105-Q105-R105-S105)</f>
       </c>
       <c r="V105" s="3">
-        <f>IF($K105="","",(U105-X105)/J105*100)</f>
+        <f>IF($K105="","",(U105-AB105)/J105*100)</f>
       </c>
       <c r="W105" s="3">
         <f>IF($K105="","",M105-T105)</f>
       </c>
-      <c r="Y105" s="3">
-        <f>IF($K105="","",U105-X105)</f>
-      </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC105" s="3">
+        <f>IF($K105="","",U105-AB105)</f>
+      </c>
+    </row>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="J106" s="3"/>
@@ -5299,16 +5323,16 @@
         <f>IF($K106="","",L106-M106-N106-Q106-R106-S106)</f>
       </c>
       <c r="V106" s="3">
-        <f>IF($K106="","",(U106-X106)/J106*100)</f>
+        <f>IF($K106="","",(U106-AB106)/J106*100)</f>
       </c>
       <c r="W106" s="3">
         <f>IF($K106="","",M106-T106)</f>
       </c>
-      <c r="Y106" s="3">
-        <f>IF($K106="","",U106-X106)</f>
-      </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC106" s="3">
+        <f>IF($K106="","",U106-AB106)</f>
+      </c>
+    </row>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="J107" s="3"/>
@@ -5342,16 +5366,16 @@
         <f>IF($K107="","",L107-M107-N107-Q107-R107-S107)</f>
       </c>
       <c r="V107" s="3">
-        <f>IF($K107="","",(U107-X107)/J107*100)</f>
+        <f>IF($K107="","",(U107-AB107)/J107*100)</f>
       </c>
       <c r="W107" s="3">
         <f>IF($K107="","",M107-T107)</f>
       </c>
-      <c r="Y107" s="3">
-        <f>IF($K107="","",U107-X107)</f>
-      </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC107" s="3">
+        <f>IF($K107="","",U107-AB107)</f>
+      </c>
+    </row>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="J108" s="3"/>
@@ -5385,16 +5409,16 @@
         <f>IF($K108="","",L108-M108-N108-Q108-R108-S108)</f>
       </c>
       <c r="V108" s="3">
-        <f>IF($K108="","",(U108-X108)/J108*100)</f>
+        <f>IF($K108="","",(U108-AB108)/J108*100)</f>
       </c>
       <c r="W108" s="3">
         <f>IF($K108="","",M108-T108)</f>
       </c>
-      <c r="Y108" s="3">
-        <f>IF($K108="","",U108-X108)</f>
-      </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC108" s="3">
+        <f>IF($K108="","",U108-AB108)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="J109" s="3"/>
@@ -5428,16 +5452,16 @@
         <f>IF($K109="","",L109-M109-N109-Q109-R109-S109)</f>
       </c>
       <c r="V109" s="3">
-        <f>IF($K109="","",(U109-X109)/J109*100)</f>
+        <f>IF($K109="","",(U109-AB109)/J109*100)</f>
       </c>
       <c r="W109" s="3">
         <f>IF($K109="","",M109-T109)</f>
       </c>
-      <c r="Y109" s="3">
-        <f>IF($K109="","",U109-X109)</f>
-      </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC109" s="3">
+        <f>IF($K109="","",U109-AB109)</f>
+      </c>
+    </row>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="J110" s="3"/>
@@ -5471,16 +5495,16 @@
         <f>IF($K110="","",L110-M110-N110-Q110-R110-S110)</f>
       </c>
       <c r="V110" s="3">
-        <f>IF($K110="","",(U110-X110)/J110*100)</f>
+        <f>IF($K110="","",(U110-AB110)/J110*100)</f>
       </c>
       <c r="W110" s="3">
         <f>IF($K110="","",M110-T110)</f>
       </c>
-      <c r="Y110" s="3">
-        <f>IF($K110="","",U110-X110)</f>
-      </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC110" s="3">
+        <f>IF($K110="","",U110-AB110)</f>
+      </c>
+    </row>
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="J111" s="3"/>
@@ -5514,16 +5538,16 @@
         <f>IF($K111="","",L111-M111-N111-Q111-R111-S111)</f>
       </c>
       <c r="V111" s="3">
-        <f>IF($K111="","",(U111-X111)/J111*100)</f>
+        <f>IF($K111="","",(U111-AB111)/J111*100)</f>
       </c>
       <c r="W111" s="3">
         <f>IF($K111="","",M111-T111)</f>
       </c>
-      <c r="Y111" s="3">
-        <f>IF($K111="","",U111-X111)</f>
-      </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC111" s="3">
+        <f>IF($K111="","",U111-AB111)</f>
+      </c>
+    </row>
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="J112" s="3"/>
@@ -5557,16 +5581,16 @@
         <f>IF($K112="","",L112-M112-N112-Q112-R112-S112)</f>
       </c>
       <c r="V112" s="3">
-        <f>IF($K112="","",(U112-X112)/J112*100)</f>
+        <f>IF($K112="","",(U112-AB112)/J112*100)</f>
       </c>
       <c r="W112" s="3">
         <f>IF($K112="","",M112-T112)</f>
       </c>
-      <c r="Y112" s="3">
-        <f>IF($K112="","",U112-X112)</f>
-      </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC112" s="3">
+        <f>IF($K112="","",U112-AB112)</f>
+      </c>
+    </row>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="J113" s="3"/>
@@ -5600,16 +5624,16 @@
         <f>IF($K113="","",L113-M113-N113-Q113-R113-S113)</f>
       </c>
       <c r="V113" s="3">
-        <f>IF($K113="","",(U113-X113)/J113*100)</f>
+        <f>IF($K113="","",(U113-AB113)/J113*100)</f>
       </c>
       <c r="W113" s="3">
         <f>IF($K113="","",M113-T113)</f>
       </c>
-      <c r="Y113" s="3">
-        <f>IF($K113="","",U113-X113)</f>
-      </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC113" s="3">
+        <f>IF($K113="","",U113-AB113)</f>
+      </c>
+    </row>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="J114" s="3"/>
@@ -5643,16 +5667,16 @@
         <f>IF($K114="","",L114-M114-N114-Q114-R114-S114)</f>
       </c>
       <c r="V114" s="3">
-        <f>IF($K114="","",(U114-X114)/J114*100)</f>
+        <f>IF($K114="","",(U114-AB114)/J114*100)</f>
       </c>
       <c r="W114" s="3">
         <f>IF($K114="","",M114-T114)</f>
       </c>
-      <c r="Y114" s="3">
-        <f>IF($K114="","",U114-X114)</f>
-      </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC114" s="3">
+        <f>IF($K114="","",U114-AB114)</f>
+      </c>
+    </row>
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="J115" s="3"/>
@@ -5686,16 +5710,16 @@
         <f>IF($K115="","",L115-M115-N115-Q115-R115-S115)</f>
       </c>
       <c r="V115" s="3">
-        <f>IF($K115="","",(U115-X115)/J115*100)</f>
+        <f>IF($K115="","",(U115-AB115)/J115*100)</f>
       </c>
       <c r="W115" s="3">
         <f>IF($K115="","",M115-T115)</f>
       </c>
-      <c r="Y115" s="3">
-        <f>IF($K115="","",U115-X115)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC115" s="3">
+        <f>IF($K115="","",U115-AB115)</f>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="J116" s="3"/>
@@ -5729,16 +5753,16 @@
         <f>IF($K116="","",L116-M116-N116-Q116-R116-S116)</f>
       </c>
       <c r="V116" s="3">
-        <f>IF($K116="","",(U116-X116)/J116*100)</f>
+        <f>IF($K116="","",(U116-AB116)/J116*100)</f>
       </c>
       <c r="W116" s="3">
         <f>IF($K116="","",M116-T116)</f>
       </c>
-      <c r="Y116" s="3">
-        <f>IF($K116="","",U116-X116)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC116" s="3">
+        <f>IF($K116="","",U116-AB116)</f>
+      </c>
+    </row>
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="J117" s="3"/>
@@ -5772,16 +5796,16 @@
         <f>IF($K117="","",L117-M117-N117-Q117-R117-S117)</f>
       </c>
       <c r="V117" s="3">
-        <f>IF($K117="","",(U117-X117)/J117*100)</f>
+        <f>IF($K117="","",(U117-AB117)/J117*100)</f>
       </c>
       <c r="W117" s="3">
         <f>IF($K117="","",M117-T117)</f>
       </c>
-      <c r="Y117" s="3">
-        <f>IF($K117="","",U117-X117)</f>
-      </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC117" s="3">
+        <f>IF($K117="","",U117-AB117)</f>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="J118" s="3"/>
@@ -5815,16 +5839,16 @@
         <f>IF($K118="","",L118-M118-N118-Q118-R118-S118)</f>
       </c>
       <c r="V118" s="3">
-        <f>IF($K118="","",(U118-X118)/J118*100)</f>
+        <f>IF($K118="","",(U118-AB118)/J118*100)</f>
       </c>
       <c r="W118" s="3">
         <f>IF($K118="","",M118-T118)</f>
       </c>
-      <c r="Y118" s="3">
-        <f>IF($K118="","",U118-X118)</f>
-      </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC118" s="3">
+        <f>IF($K118="","",U118-AB118)</f>
+      </c>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="J119" s="3"/>
@@ -5858,16 +5882,16 @@
         <f>IF($K119="","",L119-M119-N119-Q119-R119-S119)</f>
       </c>
       <c r="V119" s="3">
-        <f>IF($K119="","",(U119-X119)/J119*100)</f>
+        <f>IF($K119="","",(U119-AB119)/J119*100)</f>
       </c>
       <c r="W119" s="3">
         <f>IF($K119="","",M119-T119)</f>
       </c>
-      <c r="Y119" s="3">
-        <f>IF($K119="","",U119-X119)</f>
-      </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC119" s="3">
+        <f>IF($K119="","",U119-AB119)</f>
+      </c>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="J120" s="3"/>
@@ -5901,16 +5925,16 @@
         <f>IF($K120="","",L120-M120-N120-Q120-R120-S120)</f>
       </c>
       <c r="V120" s="3">
-        <f>IF($K120="","",(U120-X120)/J120*100)</f>
+        <f>IF($K120="","",(U120-AB120)/J120*100)</f>
       </c>
       <c r="W120" s="3">
         <f>IF($K120="","",M120-T120)</f>
       </c>
-      <c r="Y120" s="3">
-        <f>IF($K120="","",U120-X120)</f>
-      </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC120" s="3">
+        <f>IF($K120="","",U120-AB120)</f>
+      </c>
+    </row>
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="J121" s="3"/>
@@ -5944,16 +5968,16 @@
         <f>IF($K121="","",L121-M121-N121-Q121-R121-S121)</f>
       </c>
       <c r="V121" s="3">
-        <f>IF($K121="","",(U121-X121)/J121*100)</f>
+        <f>IF($K121="","",(U121-AB121)/J121*100)</f>
       </c>
       <c r="W121" s="3">
         <f>IF($K121="","",M121-T121)</f>
       </c>
-      <c r="Y121" s="3">
-        <f>IF($K121="","",U121-X121)</f>
-      </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC121" s="3">
+        <f>IF($K121="","",U121-AB121)</f>
+      </c>
+    </row>
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="J122" s="3"/>
@@ -5987,16 +6011,16 @@
         <f>IF($K122="","",L122-M122-N122-Q122-R122-S122)</f>
       </c>
       <c r="V122" s="3">
-        <f>IF($K122="","",(U122-X122)/J122*100)</f>
+        <f>IF($K122="","",(U122-AB122)/J122*100)</f>
       </c>
       <c r="W122" s="3">
         <f>IF($K122="","",M122-T122)</f>
       </c>
-      <c r="Y122" s="3">
-        <f>IF($K122="","",U122-X122)</f>
-      </c>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC122" s="3">
+        <f>IF($K122="","",U122-AB122)</f>
+      </c>
+    </row>
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="J123" s="3"/>
@@ -6030,16 +6054,16 @@
         <f>IF($K123="","",L123-M123-N123-Q123-R123-S123)</f>
       </c>
       <c r="V123" s="3">
-        <f>IF($K123="","",(U123-X123)/J123*100)</f>
+        <f>IF($K123="","",(U123-AB123)/J123*100)</f>
       </c>
       <c r="W123" s="3">
         <f>IF($K123="","",M123-T123)</f>
       </c>
-      <c r="Y123" s="3">
-        <f>IF($K123="","",U123-X123)</f>
-      </c>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC123" s="3">
+        <f>IF($K123="","",U123-AB123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="J124" s="3"/>
@@ -6073,16 +6097,16 @@
         <f>IF($K124="","",L124-M124-N124-Q124-R124-S124)</f>
       </c>
       <c r="V124" s="3">
-        <f>IF($K124="","",(U124-X124)/J124*100)</f>
+        <f>IF($K124="","",(U124-AB124)/J124*100)</f>
       </c>
       <c r="W124" s="3">
         <f>IF($K124="","",M124-T124)</f>
       </c>
-      <c r="Y124" s="3">
-        <f>IF($K124="","",U124-X124)</f>
-      </c>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC124" s="3">
+        <f>IF($K124="","",U124-AB124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="J125" s="3"/>
@@ -6116,16 +6140,16 @@
         <f>IF($K125="","",L125-M125-N125-Q125-R125-S125)</f>
       </c>
       <c r="V125" s="3">
-        <f>IF($K125="","",(U125-X125)/J125*100)</f>
+        <f>IF($K125="","",(U125-AB125)/J125*100)</f>
       </c>
       <c r="W125" s="3">
         <f>IF($K125="","",M125-T125)</f>
       </c>
-      <c r="Y125" s="3">
-        <f>IF($K125="","",U125-X125)</f>
-      </c>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC125" s="3">
+        <f>IF($K125="","",U125-AB125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="J126" s="3"/>
@@ -6159,16 +6183,16 @@
         <f>IF($K126="","",L126-M126-N126-Q126-R126-S126)</f>
       </c>
       <c r="V126" s="3">
-        <f>IF($K126="","",(U126-X126)/J126*100)</f>
+        <f>IF($K126="","",(U126-AB126)/J126*100)</f>
       </c>
       <c r="W126" s="3">
         <f>IF($K126="","",M126-T126)</f>
       </c>
-      <c r="Y126" s="3">
-        <f>IF($K126="","",U126-X126)</f>
-      </c>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC126" s="3">
+        <f>IF($K126="","",U126-AB126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="J127" s="3"/>
@@ -6202,16 +6226,16 @@
         <f>IF($K127="","",L127-M127-N127-Q127-R127-S127)</f>
       </c>
       <c r="V127" s="3">
-        <f>IF($K127="","",(U127-X127)/J127*100)</f>
+        <f>IF($K127="","",(U127-AB127)/J127*100)</f>
       </c>
       <c r="W127" s="3">
         <f>IF($K127="","",M127-T127)</f>
       </c>
-      <c r="Y127" s="3">
-        <f>IF($K127="","",U127-X127)</f>
-      </c>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC127" s="3">
+        <f>IF($K127="","",U127-AB127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="J128" s="3"/>
@@ -6245,16 +6269,16 @@
         <f>IF($K128="","",L128-M128-N128-Q128-R128-S128)</f>
       </c>
       <c r="V128" s="3">
-        <f>IF($K128="","",(U128-X128)/J128*100)</f>
+        <f>IF($K128="","",(U128-AB128)/J128*100)</f>
       </c>
       <c r="W128" s="3">
         <f>IF($K128="","",M128-T128)</f>
       </c>
-      <c r="Y128" s="3">
-        <f>IF($K128="","",U128-X128)</f>
-      </c>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC128" s="3">
+        <f>IF($K128="","",U128-AB128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="J129" s="3"/>
@@ -6288,16 +6312,16 @@
         <f>IF($K129="","",L129-M129-N129-Q129-R129-S129)</f>
       </c>
       <c r="V129" s="3">
-        <f>IF($K129="","",(U129-X129)/J129*100)</f>
+        <f>IF($K129="","",(U129-AB129)/J129*100)</f>
       </c>
       <c r="W129" s="3">
         <f>IF($K129="","",M129-T129)</f>
       </c>
-      <c r="Y129" s="3">
-        <f>IF($K129="","",U129-X129)</f>
-      </c>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC129" s="3">
+        <f>IF($K129="","",U129-AB129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="J130" s="3"/>
@@ -6331,16 +6355,16 @@
         <f>IF($K130="","",L130-M130-N130-Q130-R130-S130)</f>
       </c>
       <c r="V130" s="3">
-        <f>IF($K130="","",(U130-X130)/J130*100)</f>
+        <f>IF($K130="","",(U130-AB130)/J130*100)</f>
       </c>
       <c r="W130" s="3">
         <f>IF($K130="","",M130-T130)</f>
       </c>
-      <c r="Y130" s="3">
-        <f>IF($K130="","",U130-X130)</f>
-      </c>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC130" s="3">
+        <f>IF($K130="","",U130-AB130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="J131" s="3"/>
@@ -6374,16 +6398,16 @@
         <f>IF($K131="","",L131-M131-N131-Q131-R131-S131)</f>
       </c>
       <c r="V131" s="3">
-        <f>IF($K131="","",(U131-X131)/J131*100)</f>
+        <f>IF($K131="","",(U131-AB131)/J131*100)</f>
       </c>
       <c r="W131" s="3">
         <f>IF($K131="","",M131-T131)</f>
       </c>
-      <c r="Y131" s="3">
-        <f>IF($K131="","",U131-X131)</f>
-      </c>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC131" s="3">
+        <f>IF($K131="","",U131-AB131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="J132" s="3"/>
@@ -6417,16 +6441,16 @@
         <f>IF($K132="","",L132-M132-N132-Q132-R132-S132)</f>
       </c>
       <c r="V132" s="3">
-        <f>IF($K132="","",(U132-X132)/J132*100)</f>
+        <f>IF($K132="","",(U132-AB132)/J132*100)</f>
       </c>
       <c r="W132" s="3">
         <f>IF($K132="","",M132-T132)</f>
       </c>
-      <c r="Y132" s="3">
-        <f>IF($K132="","",U132-X132)</f>
-      </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC132" s="3">
+        <f>IF($K132="","",U132-AB132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="J133" s="3"/>
@@ -6460,16 +6484,16 @@
         <f>IF($K133="","",L133-M133-N133-Q133-R133-S133)</f>
       </c>
       <c r="V133" s="3">
-        <f>IF($K133="","",(U133-X133)/J133*100)</f>
+        <f>IF($K133="","",(U133-AB133)/J133*100)</f>
       </c>
       <c r="W133" s="3">
         <f>IF($K133="","",M133-T133)</f>
       </c>
-      <c r="Y133" s="3">
-        <f>IF($K133="","",U133-X133)</f>
-      </c>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC133" s="3">
+        <f>IF($K133="","",U133-AB133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="J134" s="3"/>
@@ -6503,16 +6527,16 @@
         <f>IF($K134="","",L134-M134-N134-Q134-R134-S134)</f>
       </c>
       <c r="V134" s="3">
-        <f>IF($K134="","",(U134-X134)/J134*100)</f>
+        <f>IF($K134="","",(U134-AB134)/J134*100)</f>
       </c>
       <c r="W134" s="3">
         <f>IF($K134="","",M134-T134)</f>
       </c>
-      <c r="Y134" s="3">
-        <f>IF($K134="","",U134-X134)</f>
-      </c>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC134" s="3">
+        <f>IF($K134="","",U134-AB134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="J135" s="3"/>
@@ -6546,16 +6570,16 @@
         <f>IF($K135="","",L135-M135-N135-Q135-R135-S135)</f>
       </c>
       <c r="V135" s="3">
-        <f>IF($K135="","",(U135-X135)/J135*100)</f>
+        <f>IF($K135="","",(U135-AB135)/J135*100)</f>
       </c>
       <c r="W135" s="3">
         <f>IF($K135="","",M135-T135)</f>
       </c>
-      <c r="Y135" s="3">
-        <f>IF($K135="","",U135-X135)</f>
-      </c>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC135" s="3">
+        <f>IF($K135="","",U135-AB135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="J136" s="3"/>
@@ -6589,16 +6613,16 @@
         <f>IF($K136="","",L136-M136-N136-Q136-R136-S136)</f>
       </c>
       <c r="V136" s="3">
-        <f>IF($K136="","",(U136-X136)/J136*100)</f>
+        <f>IF($K136="","",(U136-AB136)/J136*100)</f>
       </c>
       <c r="W136" s="3">
         <f>IF($K136="","",M136-T136)</f>
       </c>
-      <c r="Y136" s="3">
-        <f>IF($K136="","",U136-X136)</f>
-      </c>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC136" s="3">
+        <f>IF($K136="","",U136-AB136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="J137" s="3"/>
@@ -6632,16 +6656,16 @@
         <f>IF($K137="","",L137-M137-N137-Q137-R137-S137)</f>
       </c>
       <c r="V137" s="3">
-        <f>IF($K137="","",(U137-X137)/J137*100)</f>
+        <f>IF($K137="","",(U137-AB137)/J137*100)</f>
       </c>
       <c r="W137" s="3">
         <f>IF($K137="","",M137-T137)</f>
       </c>
-      <c r="Y137" s="3">
-        <f>IF($K137="","",U137-X137)</f>
-      </c>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC137" s="3">
+        <f>IF($K137="","",U137-AB137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="J138" s="3"/>
@@ -6675,16 +6699,16 @@
         <f>IF($K138="","",L138-M138-N138-Q138-R138-S138)</f>
       </c>
       <c r="V138" s="3">
-        <f>IF($K138="","",(U138-X138)/J138*100)</f>
+        <f>IF($K138="","",(U138-AB138)/J138*100)</f>
       </c>
       <c r="W138" s="3">
         <f>IF($K138="","",M138-T138)</f>
       </c>
-      <c r="Y138" s="3">
-        <f>IF($K138="","",U138-X138)</f>
-      </c>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC138" s="3">
+        <f>IF($K138="","",U138-AB138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="J139" s="3"/>
@@ -6718,16 +6742,16 @@
         <f>IF($K139="","",L139-M139-N139-Q139-R139-S139)</f>
       </c>
       <c r="V139" s="3">
-        <f>IF($K139="","",(U139-X139)/J139*100)</f>
+        <f>IF($K139="","",(U139-AB139)/J139*100)</f>
       </c>
       <c r="W139" s="3">
         <f>IF($K139="","",M139-T139)</f>
       </c>
-      <c r="Y139" s="3">
-        <f>IF($K139="","",U139-X139)</f>
-      </c>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC139" s="3">
+        <f>IF($K139="","",U139-AB139)</f>
+      </c>
+    </row>
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="J140" s="3"/>
@@ -6761,16 +6785,16 @@
         <f>IF($K140="","",L140-M140-N140-Q140-R140-S140)</f>
       </c>
       <c r="V140" s="3">
-        <f>IF($K140="","",(U140-X140)/J140*100)</f>
+        <f>IF($K140="","",(U140-AB140)/J140*100)</f>
       </c>
       <c r="W140" s="3">
         <f>IF($K140="","",M140-T140)</f>
       </c>
-      <c r="Y140" s="3">
-        <f>IF($K140="","",U140-X140)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC140" s="3">
+        <f>IF($K140="","",U140-AB140)</f>
+      </c>
+    </row>
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="J141" s="3"/>
@@ -6804,16 +6828,16 @@
         <f>IF($K141="","",L141-M141-N141-Q141-R141-S141)</f>
       </c>
       <c r="V141" s="3">
-        <f>IF($K141="","",(U141-X141)/J141*100)</f>
+        <f>IF($K141="","",(U141-AB141)/J141*100)</f>
       </c>
       <c r="W141" s="3">
         <f>IF($K141="","",M141-T141)</f>
       </c>
-      <c r="Y141" s="3">
-        <f>IF($K141="","",U141-X141)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC141" s="3">
+        <f>IF($K141="","",U141-AB141)</f>
+      </c>
+    </row>
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="J142" s="3"/>
@@ -6847,16 +6871,16 @@
         <f>IF($K142="","",L142-M142-N142-Q142-R142-S142)</f>
       </c>
       <c r="V142" s="3">
-        <f>IF($K142="","",(U142-X142)/J142*100)</f>
+        <f>IF($K142="","",(U142-AB142)/J142*100)</f>
       </c>
       <c r="W142" s="3">
         <f>IF($K142="","",M142-T142)</f>
       </c>
-      <c r="Y142" s="3">
-        <f>IF($K142="","",U142-X142)</f>
-      </c>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC142" s="3">
+        <f>IF($K142="","",U142-AB142)</f>
+      </c>
+    </row>
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="J143" s="3"/>
@@ -6890,16 +6914,16 @@
         <f>IF($K143="","",L143-M143-N143-Q143-R143-S143)</f>
       </c>
       <c r="V143" s="3">
-        <f>IF($K143="","",(U143-X143)/J143*100)</f>
+        <f>IF($K143="","",(U143-AB143)/J143*100)</f>
       </c>
       <c r="W143" s="3">
         <f>IF($K143="","",M143-T143)</f>
       </c>
-      <c r="Y143" s="3">
-        <f>IF($K143="","",U143-X143)</f>
-      </c>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC143" s="3">
+        <f>IF($K143="","",U143-AB143)</f>
+      </c>
+    </row>
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="J144" s="3"/>
@@ -6933,16 +6957,16 @@
         <f>IF($K144="","",L144-M144-N144-Q144-R144-S144)</f>
       </c>
       <c r="V144" s="3">
-        <f>IF($K144="","",(U144-X144)/J144*100)</f>
+        <f>IF($K144="","",(U144-AB144)/J144*100)</f>
       </c>
       <c r="W144" s="3">
         <f>IF($K144="","",M144-T144)</f>
       </c>
-      <c r="Y144" s="3">
-        <f>IF($K144="","",U144-X144)</f>
-      </c>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC144" s="3">
+        <f>IF($K144="","",U144-AB144)</f>
+      </c>
+    </row>
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="J145" s="3"/>
@@ -6976,16 +7000,16 @@
         <f>IF($K145="","",L145-M145-N145-Q145-R145-S145)</f>
       </c>
       <c r="V145" s="3">
-        <f>IF($K145="","",(U145-X145)/J145*100)</f>
+        <f>IF($K145="","",(U145-AB145)/J145*100)</f>
       </c>
       <c r="W145" s="3">
         <f>IF($K145="","",M145-T145)</f>
       </c>
-      <c r="Y145" s="3">
-        <f>IF($K145="","",U145-X145)</f>
-      </c>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC145" s="3">
+        <f>IF($K145="","",U145-AB145)</f>
+      </c>
+    </row>
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="J146" s="3"/>
@@ -7019,16 +7043,16 @@
         <f>IF($K146="","",L146-M146-N146-Q146-R146-S146)</f>
       </c>
       <c r="V146" s="3">
-        <f>IF($K146="","",(U146-X146)/J146*100)</f>
+        <f>IF($K146="","",(U146-AB146)/J146*100)</f>
       </c>
       <c r="W146" s="3">
         <f>IF($K146="","",M146-T146)</f>
       </c>
-      <c r="Y146" s="3">
-        <f>IF($K146="","",U146-X146)</f>
-      </c>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC146" s="3">
+        <f>IF($K146="","",U146-AB146)</f>
+      </c>
+    </row>
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="J147" s="3"/>
@@ -7062,16 +7086,16 @@
         <f>IF($K147="","",L147-M147-N147-Q147-R147-S147)</f>
       </c>
       <c r="V147" s="3">
-        <f>IF($K147="","",(U147-X147)/J147*100)</f>
+        <f>IF($K147="","",(U147-AB147)/J147*100)</f>
       </c>
       <c r="W147" s="3">
         <f>IF($K147="","",M147-T147)</f>
       </c>
-      <c r="Y147" s="3">
-        <f>IF($K147="","",U147-X147)</f>
-      </c>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC147" s="3">
+        <f>IF($K147="","",U147-AB147)</f>
+      </c>
+    </row>
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="J148" s="3"/>
@@ -7105,16 +7129,16 @@
         <f>IF($K148="","",L148-M148-N148-Q148-R148-S148)</f>
       </c>
       <c r="V148" s="3">
-        <f>IF($K148="","",(U148-X148)/J148*100)</f>
+        <f>IF($K148="","",(U148-AB148)/J148*100)</f>
       </c>
       <c r="W148" s="3">
         <f>IF($K148="","",M148-T148)</f>
       </c>
-      <c r="Y148" s="3">
-        <f>IF($K148="","",U148-X148)</f>
-      </c>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC148" s="3">
+        <f>IF($K148="","",U148-AB148)</f>
+      </c>
+    </row>
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="J149" s="3"/>
@@ -7148,16 +7172,16 @@
         <f>IF($K149="","",L149-M149-N149-Q149-R149-S149)</f>
       </c>
       <c r="V149" s="3">
-        <f>IF($K149="","",(U149-X149)/J149*100)</f>
+        <f>IF($K149="","",(U149-AB149)/J149*100)</f>
       </c>
       <c r="W149" s="3">
         <f>IF($K149="","",M149-T149)</f>
       </c>
-      <c r="Y149" s="3">
-        <f>IF($K149="","",U149-X149)</f>
-      </c>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC149" s="3">
+        <f>IF($K149="","",U149-AB149)</f>
+      </c>
+    </row>
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="J150" s="3"/>
@@ -7191,16 +7215,16 @@
         <f>IF($K150="","",L150-M150-N150-Q150-R150-S150)</f>
       </c>
       <c r="V150" s="3">
-        <f>IF($K150="","",(U150-X150)/J150*100)</f>
+        <f>IF($K150="","",(U150-AB150)/J150*100)</f>
       </c>
       <c r="W150" s="3">
         <f>IF($K150="","",M150-T150)</f>
       </c>
-      <c r="Y150" s="3">
-        <f>IF($K150="","",U150-X150)</f>
-      </c>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC150" s="3">
+        <f>IF($K150="","",U150-AB150)</f>
+      </c>
+    </row>
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="J151" s="3"/>
@@ -7234,16 +7258,16 @@
         <f>IF($K151="","",L151-M151-N151-Q151-R151-S151)</f>
       </c>
       <c r="V151" s="3">
-        <f>IF($K151="","",(U151-X151)/J151*100)</f>
+        <f>IF($K151="","",(U151-AB151)/J151*100)</f>
       </c>
       <c r="W151" s="3">
         <f>IF($K151="","",M151-T151)</f>
       </c>
-      <c r="Y151" s="3">
-        <f>IF($K151="","",U151-X151)</f>
-      </c>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC151" s="3">
+        <f>IF($K151="","",U151-AB151)</f>
+      </c>
+    </row>
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="J152" s="3"/>
@@ -7277,16 +7301,16 @@
         <f>IF($K152="","",L152-M152-N152-Q152-R152-S152)</f>
       </c>
       <c r="V152" s="3">
-        <f>IF($K152="","",(U152-X152)/J152*100)</f>
+        <f>IF($K152="","",(U152-AB152)/J152*100)</f>
       </c>
       <c r="W152" s="3">
         <f>IF($K152="","",M152-T152)</f>
       </c>
-      <c r="Y152" s="3">
-        <f>IF($K152="","",U152-X152)</f>
-      </c>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC152" s="3">
+        <f>IF($K152="","",U152-AB152)</f>
+      </c>
+    </row>
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="J153" s="3"/>
@@ -7320,16 +7344,16 @@
         <f>IF($K153="","",L153-M153-N153-Q153-R153-S153)</f>
       </c>
       <c r="V153" s="3">
-        <f>IF($K153="","",(U153-X153)/J153*100)</f>
+        <f>IF($K153="","",(U153-AB153)/J153*100)</f>
       </c>
       <c r="W153" s="3">
         <f>IF($K153="","",M153-T153)</f>
       </c>
-      <c r="Y153" s="3">
-        <f>IF($K153="","",U153-X153)</f>
-      </c>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC153" s="3">
+        <f>IF($K153="","",U153-AB153)</f>
+      </c>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="J154" s="3"/>
@@ -7363,16 +7387,16 @@
         <f>IF($K154="","",L154-M154-N154-Q154-R154-S154)</f>
       </c>
       <c r="V154" s="3">
-        <f>IF($K154="","",(U154-X154)/J154*100)</f>
+        <f>IF($K154="","",(U154-AB154)/J154*100)</f>
       </c>
       <c r="W154" s="3">
         <f>IF($K154="","",M154-T154)</f>
       </c>
-      <c r="Y154" s="3">
-        <f>IF($K154="","",U154-X154)</f>
-      </c>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC154" s="3">
+        <f>IF($K154="","",U154-AB154)</f>
+      </c>
+    </row>
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="J155" s="3"/>
@@ -7406,16 +7430,16 @@
         <f>IF($K155="","",L155-M155-N155-Q155-R155-S155)</f>
       </c>
       <c r="V155" s="3">
-        <f>IF($K155="","",(U155-X155)/J155*100)</f>
+        <f>IF($K155="","",(U155-AB155)/J155*100)</f>
       </c>
       <c r="W155" s="3">
         <f>IF($K155="","",M155-T155)</f>
       </c>
-      <c r="Y155" s="3">
-        <f>IF($K155="","",U155-X155)</f>
-      </c>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC155" s="3">
+        <f>IF($K155="","",U155-AB155)</f>
+      </c>
+    </row>
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="J156" s="3"/>
@@ -7449,16 +7473,16 @@
         <f>IF($K156="","",L156-M156-N156-Q156-R156-S156)</f>
       </c>
       <c r="V156" s="3">
-        <f>IF($K156="","",(U156-X156)/J156*100)</f>
+        <f>IF($K156="","",(U156-AB156)/J156*100)</f>
       </c>
       <c r="W156" s="3">
         <f>IF($K156="","",M156-T156)</f>
       </c>
-      <c r="Y156" s="3">
-        <f>IF($K156="","",U156-X156)</f>
-      </c>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC156" s="3">
+        <f>IF($K156="","",U156-AB156)</f>
+      </c>
+    </row>
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="J157" s="3"/>
@@ -7492,16 +7516,16 @@
         <f>IF($K157="","",L157-M157-N157-Q157-R157-S157)</f>
       </c>
       <c r="V157" s="3">
-        <f>IF($K157="","",(U157-X157)/J157*100)</f>
+        <f>IF($K157="","",(U157-AB157)/J157*100)</f>
       </c>
       <c r="W157" s="3">
         <f>IF($K157="","",M157-T157)</f>
       </c>
-      <c r="Y157" s="3">
-        <f>IF($K157="","",U157-X157)</f>
-      </c>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC157" s="3">
+        <f>IF($K157="","",U157-AB157)</f>
+      </c>
+    </row>
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="J158" s="3"/>
@@ -7535,16 +7559,16 @@
         <f>IF($K158="","",L158-M158-N158-Q158-R158-S158)</f>
       </c>
       <c r="V158" s="3">
-        <f>IF($K158="","",(U158-X158)/J158*100)</f>
+        <f>IF($K158="","",(U158-AB158)/J158*100)</f>
       </c>
       <c r="W158" s="3">
         <f>IF($K158="","",M158-T158)</f>
       </c>
-      <c r="Y158" s="3">
-        <f>IF($K158="","",U158-X158)</f>
-      </c>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC158" s="3">
+        <f>IF($K158="","",U158-AB158)</f>
+      </c>
+    </row>
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="J159" s="3"/>
@@ -7578,16 +7602,16 @@
         <f>IF($K159="","",L159-M159-N159-Q159-R159-S159)</f>
       </c>
       <c r="V159" s="3">
-        <f>IF($K159="","",(U159-X159)/J159*100)</f>
+        <f>IF($K159="","",(U159-AB159)/J159*100)</f>
       </c>
       <c r="W159" s="3">
         <f>IF($K159="","",M159-T159)</f>
       </c>
-      <c r="Y159" s="3">
-        <f>IF($K159="","",U159-X159)</f>
-      </c>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC159" s="3">
+        <f>IF($K159="","",U159-AB159)</f>
+      </c>
+    </row>
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="J160" s="3"/>
@@ -7621,16 +7645,16 @@
         <f>IF($K160="","",L160-M160-N160-Q160-R160-S160)</f>
       </c>
       <c r="V160" s="3">
-        <f>IF($K160="","",(U160-X160)/J160*100)</f>
+        <f>IF($K160="","",(U160-AB160)/J160*100)</f>
       </c>
       <c r="W160" s="3">
         <f>IF($K160="","",M160-T160)</f>
       </c>
-      <c r="Y160" s="3">
-        <f>IF($K160="","",U160-X160)</f>
-      </c>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC160" s="3">
+        <f>IF($K160="","",U160-AB160)</f>
+      </c>
+    </row>
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="J161" s="3"/>
@@ -7664,16 +7688,16 @@
         <f>IF($K161="","",L161-M161-N161-Q161-R161-S161)</f>
       </c>
       <c r="V161" s="3">
-        <f>IF($K161="","",(U161-X161)/J161*100)</f>
+        <f>IF($K161="","",(U161-AB161)/J161*100)</f>
       </c>
       <c r="W161" s="3">
         <f>IF($K161="","",M161-T161)</f>
       </c>
-      <c r="Y161" s="3">
-        <f>IF($K161="","",U161-X161)</f>
-      </c>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC161" s="3">
+        <f>IF($K161="","",U161-AB161)</f>
+      </c>
+    </row>
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="J162" s="3"/>
@@ -7707,16 +7731,16 @@
         <f>IF($K162="","",L162-M162-N162-Q162-R162-S162)</f>
       </c>
       <c r="V162" s="3">
-        <f>IF($K162="","",(U162-X162)/J162*100)</f>
+        <f>IF($K162="","",(U162-AB162)/J162*100)</f>
       </c>
       <c r="W162" s="3">
         <f>IF($K162="","",M162-T162)</f>
       </c>
-      <c r="Y162" s="3">
-        <f>IF($K162="","",U162-X162)</f>
-      </c>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC162" s="3">
+        <f>IF($K162="","",U162-AB162)</f>
+      </c>
+    </row>
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="J163" s="3"/>
@@ -7750,16 +7774,16 @@
         <f>IF($K163="","",L163-M163-N163-Q163-R163-S163)</f>
       </c>
       <c r="V163" s="3">
-        <f>IF($K163="","",(U163-X163)/J163*100)</f>
+        <f>IF($K163="","",(U163-AB163)/J163*100)</f>
       </c>
       <c r="W163" s="3">
         <f>IF($K163="","",M163-T163)</f>
       </c>
-      <c r="Y163" s="3">
-        <f>IF($K163="","",U163-X163)</f>
-      </c>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC163" s="3">
+        <f>IF($K163="","",U163-AB163)</f>
+      </c>
+    </row>
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="J164" s="3"/>
@@ -7793,16 +7817,16 @@
         <f>IF($K164="","",L164-M164-N164-Q164-R164-S164)</f>
       </c>
       <c r="V164" s="3">
-        <f>IF($K164="","",(U164-X164)/J164*100)</f>
+        <f>IF($K164="","",(U164-AB164)/J164*100)</f>
       </c>
       <c r="W164" s="3">
         <f>IF($K164="","",M164-T164)</f>
       </c>
-      <c r="Y164" s="3">
-        <f>IF($K164="","",U164-X164)</f>
-      </c>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC164" s="3">
+        <f>IF($K164="","",U164-AB164)</f>
+      </c>
+    </row>
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="J165" s="3"/>
@@ -7836,16 +7860,16 @@
         <f>IF($K165="","",L165-M165-N165-Q165-R165-S165)</f>
       </c>
       <c r="V165" s="3">
-        <f>IF($K165="","",(U165-X165)/J165*100)</f>
+        <f>IF($K165="","",(U165-AB165)/J165*100)</f>
       </c>
       <c r="W165" s="3">
         <f>IF($K165="","",M165-T165)</f>
       </c>
-      <c r="Y165" s="3">
-        <f>IF($K165="","",U165-X165)</f>
-      </c>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC165" s="3">
+        <f>IF($K165="","",U165-AB165)</f>
+      </c>
+    </row>
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="J166" s="3"/>
@@ -7879,16 +7903,16 @@
         <f>IF($K166="","",L166-M166-N166-Q166-R166-S166)</f>
       </c>
       <c r="V166" s="3">
-        <f>IF($K166="","",(U166-X166)/J166*100)</f>
+        <f>IF($K166="","",(U166-AB166)/J166*100)</f>
       </c>
       <c r="W166" s="3">
         <f>IF($K166="","",M166-T166)</f>
       </c>
-      <c r="Y166" s="3">
-        <f>IF($K166="","",U166-X166)</f>
-      </c>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC166" s="3">
+        <f>IF($K166="","",U166-AB166)</f>
+      </c>
+    </row>
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="J167" s="3"/>
@@ -7922,16 +7946,16 @@
         <f>IF($K167="","",L167-M167-N167-Q167-R167-S167)</f>
       </c>
       <c r="V167" s="3">
-        <f>IF($K167="","",(U167-X167)/J167*100)</f>
+        <f>IF($K167="","",(U167-AB167)/J167*100)</f>
       </c>
       <c r="W167" s="3">
         <f>IF($K167="","",M167-T167)</f>
       </c>
-      <c r="Y167" s="3">
-        <f>IF($K167="","",U167-X167)</f>
-      </c>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC167" s="3">
+        <f>IF($K167="","",U167-AB167)</f>
+      </c>
+    </row>
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="J168" s="3"/>
@@ -7965,16 +7989,16 @@
         <f>IF($K168="","",L168-M168-N168-Q168-R168-S168)</f>
       </c>
       <c r="V168" s="3">
-        <f>IF($K168="","",(U168-X168)/J168*100)</f>
+        <f>IF($K168="","",(U168-AB168)/J168*100)</f>
       </c>
       <c r="W168" s="3">
         <f>IF($K168="","",M168-T168)</f>
       </c>
-      <c r="Y168" s="3">
-        <f>IF($K168="","",U168-X168)</f>
-      </c>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC168" s="3">
+        <f>IF($K168="","",U168-AB168)</f>
+      </c>
+    </row>
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="J169" s="3"/>
@@ -8008,16 +8032,16 @@
         <f>IF($K169="","",L169-M169-N169-Q169-R169-S169)</f>
       </c>
       <c r="V169" s="3">
-        <f>IF($K169="","",(U169-X169)/J169*100)</f>
+        <f>IF($K169="","",(U169-AB169)/J169*100)</f>
       </c>
       <c r="W169" s="3">
         <f>IF($K169="","",M169-T169)</f>
       </c>
-      <c r="Y169" s="3">
-        <f>IF($K169="","",U169-X169)</f>
-      </c>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC169" s="3">
+        <f>IF($K169="","",U169-AB169)</f>
+      </c>
+    </row>
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="J170" s="3"/>
@@ -8051,16 +8075,16 @@
         <f>IF($K170="","",L170-M170-N170-Q170-R170-S170)</f>
       </c>
       <c r="V170" s="3">
-        <f>IF($K170="","",(U170-X170)/J170*100)</f>
+        <f>IF($K170="","",(U170-AB170)/J170*100)</f>
       </c>
       <c r="W170" s="3">
         <f>IF($K170="","",M170-T170)</f>
       </c>
-      <c r="Y170" s="3">
-        <f>IF($K170="","",U170-X170)</f>
-      </c>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC170" s="3">
+        <f>IF($K170="","",U170-AB170)</f>
+      </c>
+    </row>
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="J171" s="3"/>
@@ -8094,16 +8118,16 @@
         <f>IF($K171="","",L171-M171-N171-Q171-R171-S171)</f>
       </c>
       <c r="V171" s="3">
-        <f>IF($K171="","",(U171-X171)/J171*100)</f>
+        <f>IF($K171="","",(U171-AB171)/J171*100)</f>
       </c>
       <c r="W171" s="3">
         <f>IF($K171="","",M171-T171)</f>
       </c>
-      <c r="Y171" s="3">
-        <f>IF($K171="","",U171-X171)</f>
-      </c>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC171" s="3">
+        <f>IF($K171="","",U171-AB171)</f>
+      </c>
+    </row>
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="J172" s="3"/>
@@ -8137,16 +8161,16 @@
         <f>IF($K172="","",L172-M172-N172-Q172-R172-S172)</f>
       </c>
       <c r="V172" s="3">
-        <f>IF($K172="","",(U172-X172)/J172*100)</f>
+        <f>IF($K172="","",(U172-AB172)/J172*100)</f>
       </c>
       <c r="W172" s="3">
         <f>IF($K172="","",M172-T172)</f>
       </c>
-      <c r="Y172" s="3">
-        <f>IF($K172="","",U172-X172)</f>
-      </c>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC172" s="3">
+        <f>IF($K172="","",U172-AB172)</f>
+      </c>
+    </row>
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="J173" s="3"/>
@@ -8180,16 +8204,16 @@
         <f>IF($K173="","",L173-M173-N173-Q173-R173-S173)</f>
       </c>
       <c r="V173" s="3">
-        <f>IF($K173="","",(U173-X173)/J173*100)</f>
+        <f>IF($K173="","",(U173-AB173)/J173*100)</f>
       </c>
       <c r="W173" s="3">
         <f>IF($K173="","",M173-T173)</f>
       </c>
-      <c r="Y173" s="3">
-        <f>IF($K173="","",U173-X173)</f>
-      </c>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC173" s="3">
+        <f>IF($K173="","",U173-AB173)</f>
+      </c>
+    </row>
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="J174" s="3"/>
@@ -8223,16 +8247,16 @@
         <f>IF($K174="","",L174-M174-N174-Q174-R174-S174)</f>
       </c>
       <c r="V174" s="3">
-        <f>IF($K174="","",(U174-X174)/J174*100)</f>
+        <f>IF($K174="","",(U174-AB174)/J174*100)</f>
       </c>
       <c r="W174" s="3">
         <f>IF($K174="","",M174-T174)</f>
       </c>
-      <c r="Y174" s="3">
-        <f>IF($K174="","",U174-X174)</f>
-      </c>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC174" s="3">
+        <f>IF($K174="","",U174-AB174)</f>
+      </c>
+    </row>
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="J175" s="3"/>
@@ -8266,16 +8290,16 @@
         <f>IF($K175="","",L175-M175-N175-Q175-R175-S175)</f>
       </c>
       <c r="V175" s="3">
-        <f>IF($K175="","",(U175-X175)/J175*100)</f>
+        <f>IF($K175="","",(U175-AB175)/J175*100)</f>
       </c>
       <c r="W175" s="3">
         <f>IF($K175="","",M175-T175)</f>
       </c>
-      <c r="Y175" s="3">
-        <f>IF($K175="","",U175-X175)</f>
-      </c>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC175" s="3">
+        <f>IF($K175="","",U175-AB175)</f>
+      </c>
+    </row>
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="J176" s="3"/>
@@ -8309,16 +8333,16 @@
         <f>IF($K176="","",L176-M176-N176-Q176-R176-S176)</f>
       </c>
       <c r="V176" s="3">
-        <f>IF($K176="","",(U176-X176)/J176*100)</f>
+        <f>IF($K176="","",(U176-AB176)/J176*100)</f>
       </c>
       <c r="W176" s="3">
         <f>IF($K176="","",M176-T176)</f>
       </c>
-      <c r="Y176" s="3">
-        <f>IF($K176="","",U176-X176)</f>
-      </c>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC176" s="3">
+        <f>IF($K176="","",U176-AB176)</f>
+      </c>
+    </row>
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="J177" s="3"/>
@@ -8352,16 +8376,16 @@
         <f>IF($K177="","",L177-M177-N177-Q177-R177-S177)</f>
       </c>
       <c r="V177" s="3">
-        <f>IF($K177="","",(U177-X177)/J177*100)</f>
+        <f>IF($K177="","",(U177-AB177)/J177*100)</f>
       </c>
       <c r="W177" s="3">
         <f>IF($K177="","",M177-T177)</f>
       </c>
-      <c r="Y177" s="3">
-        <f>IF($K177="","",U177-X177)</f>
-      </c>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC177" s="3">
+        <f>IF($K177="","",U177-AB177)</f>
+      </c>
+    </row>
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="J178" s="3"/>
@@ -8395,16 +8419,16 @@
         <f>IF($K178="","",L178-M178-N178-Q178-R178-S178)</f>
       </c>
       <c r="V178" s="3">
-        <f>IF($K178="","",(U178-X178)/J178*100)</f>
+        <f>IF($K178="","",(U178-AB178)/J178*100)</f>
       </c>
       <c r="W178" s="3">
         <f>IF($K178="","",M178-T178)</f>
       </c>
-      <c r="Y178" s="3">
-        <f>IF($K178="","",U178-X178)</f>
-      </c>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC178" s="3">
+        <f>IF($K178="","",U178-AB178)</f>
+      </c>
+    </row>
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="J179" s="3"/>
@@ -8438,16 +8462,16 @@
         <f>IF($K179="","",L179-M179-N179-Q179-R179-S179)</f>
       </c>
       <c r="V179" s="3">
-        <f>IF($K179="","",(U179-X179)/J179*100)</f>
+        <f>IF($K179="","",(U179-AB179)/J179*100)</f>
       </c>
       <c r="W179" s="3">
         <f>IF($K179="","",M179-T179)</f>
       </c>
-      <c r="Y179" s="3">
-        <f>IF($K179="","",U179-X179)</f>
-      </c>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC179" s="3">
+        <f>IF($K179="","",U179-AB179)</f>
+      </c>
+    </row>
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="J180" s="3"/>
@@ -8481,16 +8505,16 @@
         <f>IF($K180="","",L180-M180-N180-Q180-R180-S180)</f>
       </c>
       <c r="V180" s="3">
-        <f>IF($K180="","",(U180-X180)/J180*100)</f>
+        <f>IF($K180="","",(U180-AB180)/J180*100)</f>
       </c>
       <c r="W180" s="3">
         <f>IF($K180="","",M180-T180)</f>
       </c>
-      <c r="Y180" s="3">
-        <f>IF($K180="","",U180-X180)</f>
-      </c>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC180" s="3">
+        <f>IF($K180="","",U180-AB180)</f>
+      </c>
+    </row>
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="J181" s="3"/>
@@ -8524,16 +8548,16 @@
         <f>IF($K181="","",L181-M181-N181-Q181-R181-S181)</f>
       </c>
       <c r="V181" s="3">
-        <f>IF($K181="","",(U181-X181)/J181*100)</f>
+        <f>IF($K181="","",(U181-AB181)/J181*100)</f>
       </c>
       <c r="W181" s="3">
         <f>IF($K181="","",M181-T181)</f>
       </c>
-      <c r="Y181" s="3">
-        <f>IF($K181="","",U181-X181)</f>
-      </c>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC181" s="3">
+        <f>IF($K181="","",U181-AB181)</f>
+      </c>
+    </row>
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="J182" s="3"/>
@@ -8567,16 +8591,16 @@
         <f>IF($K182="","",L182-M182-N182-Q182-R182-S182)</f>
       </c>
       <c r="V182" s="3">
-        <f>IF($K182="","",(U182-X182)/J182*100)</f>
+        <f>IF($K182="","",(U182-AB182)/J182*100)</f>
       </c>
       <c r="W182" s="3">
         <f>IF($K182="","",M182-T182)</f>
       </c>
-      <c r="Y182" s="3">
-        <f>IF($K182="","",U182-X182)</f>
-      </c>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC182" s="3">
+        <f>IF($K182="","",U182-AB182)</f>
+      </c>
+    </row>
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="J183" s="3"/>
@@ -8610,16 +8634,16 @@
         <f>IF($K183="","",L183-M183-N183-Q183-R183-S183)</f>
       </c>
       <c r="V183" s="3">
-        <f>IF($K183="","",(U183-X183)/J183*100)</f>
+        <f>IF($K183="","",(U183-AB183)/J183*100)</f>
       </c>
       <c r="W183" s="3">
         <f>IF($K183="","",M183-T183)</f>
       </c>
-      <c r="Y183" s="3">
-        <f>IF($K183="","",U183-X183)</f>
-      </c>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC183" s="3">
+        <f>IF($K183="","",U183-AB183)</f>
+      </c>
+    </row>
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="J184" s="3"/>
@@ -8653,16 +8677,16 @@
         <f>IF($K184="","",L184-M184-N184-Q184-R184-S184)</f>
       </c>
       <c r="V184" s="3">
-        <f>IF($K184="","",(U184-X184)/J184*100)</f>
+        <f>IF($K184="","",(U184-AB184)/J184*100)</f>
       </c>
       <c r="W184" s="3">
         <f>IF($K184="","",M184-T184)</f>
       </c>
-      <c r="Y184" s="3">
-        <f>IF($K184="","",U184-X184)</f>
-      </c>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC184" s="3">
+        <f>IF($K184="","",U184-AB184)</f>
+      </c>
+    </row>
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="J185" s="3"/>
@@ -8696,16 +8720,16 @@
         <f>IF($K185="","",L185-M185-N185-Q185-R185-S185)</f>
       </c>
       <c r="V185" s="3">
-        <f>IF($K185="","",(U185-X185)/J185*100)</f>
+        <f>IF($K185="","",(U185-AB185)/J185*100)</f>
       </c>
       <c r="W185" s="3">
         <f>IF($K185="","",M185-T185)</f>
       </c>
-      <c r="Y185" s="3">
-        <f>IF($K185="","",U185-X185)</f>
-      </c>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC185" s="3">
+        <f>IF($K185="","",U185-AB185)</f>
+      </c>
+    </row>
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="J186" s="3"/>
@@ -8739,16 +8763,16 @@
         <f>IF($K186="","",L186-M186-N186-Q186-R186-S186)</f>
       </c>
       <c r="V186" s="3">
-        <f>IF($K186="","",(U186-X186)/J186*100)</f>
+        <f>IF($K186="","",(U186-AB186)/J186*100)</f>
       </c>
       <c r="W186" s="3">
         <f>IF($K186="","",M186-T186)</f>
       </c>
-      <c r="Y186" s="3">
-        <f>IF($K186="","",U186-X186)</f>
-      </c>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC186" s="3">
+        <f>IF($K186="","",U186-AB186)</f>
+      </c>
+    </row>
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="J187" s="3"/>
@@ -8782,16 +8806,16 @@
         <f>IF($K187="","",L187-M187-N187-Q187-R187-S187)</f>
       </c>
       <c r="V187" s="3">
-        <f>IF($K187="","",(U187-X187)/J187*100)</f>
+        <f>IF($K187="","",(U187-AB187)/J187*100)</f>
       </c>
       <c r="W187" s="3">
         <f>IF($K187="","",M187-T187)</f>
       </c>
-      <c r="Y187" s="3">
-        <f>IF($K187="","",U187-X187)</f>
-      </c>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC187" s="3">
+        <f>IF($K187="","",U187-AB187)</f>
+      </c>
+    </row>
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="J188" s="3"/>
@@ -8825,16 +8849,16 @@
         <f>IF($K188="","",L188-M188-N188-Q188-R188-S188)</f>
       </c>
       <c r="V188" s="3">
-        <f>IF($K188="","",(U188-X188)/J188*100)</f>
+        <f>IF($K188="","",(U188-AB188)/J188*100)</f>
       </c>
       <c r="W188" s="3">
         <f>IF($K188="","",M188-T188)</f>
       </c>
-      <c r="Y188" s="3">
-        <f>IF($K188="","",U188-X188)</f>
-      </c>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC188" s="3">
+        <f>IF($K188="","",U188-AB188)</f>
+      </c>
+    </row>
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="J189" s="3"/>
@@ -8868,16 +8892,16 @@
         <f>IF($K189="","",L189-M189-N189-Q189-R189-S189)</f>
       </c>
       <c r="V189" s="3">
-        <f>IF($K189="","",(U189-X189)/J189*100)</f>
+        <f>IF($K189="","",(U189-AB189)/J189*100)</f>
       </c>
       <c r="W189" s="3">
         <f>IF($K189="","",M189-T189)</f>
       </c>
-      <c r="Y189" s="3">
-        <f>IF($K189="","",U189-X189)</f>
-      </c>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC189" s="3">
+        <f>IF($K189="","",U189-AB189)</f>
+      </c>
+    </row>
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="J190" s="3"/>
@@ -8911,16 +8935,16 @@
         <f>IF($K190="","",L190-M190-N190-Q190-R190-S190)</f>
       </c>
       <c r="V190" s="3">
-        <f>IF($K190="","",(U190-X190)/J190*100)</f>
+        <f>IF($K190="","",(U190-AB190)/J190*100)</f>
       </c>
       <c r="W190" s="3">
         <f>IF($K190="","",M190-T190)</f>
       </c>
-      <c r="Y190" s="3">
-        <f>IF($K190="","",U190-X190)</f>
-      </c>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC190" s="3">
+        <f>IF($K190="","",U190-AB190)</f>
+      </c>
+    </row>
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="J191" s="3"/>
@@ -8954,16 +8978,16 @@
         <f>IF($K191="","",L191-M191-N191-Q191-R191-S191)</f>
       </c>
       <c r="V191" s="3">
-        <f>IF($K191="","",(U191-X191)/J191*100)</f>
+        <f>IF($K191="","",(U191-AB191)/J191*100)</f>
       </c>
       <c r="W191" s="3">
         <f>IF($K191="","",M191-T191)</f>
       </c>
-      <c r="Y191" s="3">
-        <f>IF($K191="","",U191-X191)</f>
-      </c>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC191" s="3">
+        <f>IF($K191="","",U191-AB191)</f>
+      </c>
+    </row>
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="J192" s="3"/>
@@ -8997,16 +9021,16 @@
         <f>IF($K192="","",L192-M192-N192-Q192-R192-S192)</f>
       </c>
       <c r="V192" s="3">
-        <f>IF($K192="","",(U192-X192)/J192*100)</f>
+        <f>IF($K192="","",(U192-AB192)/J192*100)</f>
       </c>
       <c r="W192" s="3">
         <f>IF($K192="","",M192-T192)</f>
       </c>
-      <c r="Y192" s="3">
-        <f>IF($K192="","",U192-X192)</f>
-      </c>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC192" s="3">
+        <f>IF($K192="","",U192-AB192)</f>
+      </c>
+    </row>
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="J193" s="3"/>
@@ -9040,16 +9064,16 @@
         <f>IF($K193="","",L193-M193-N193-Q193-R193-S193)</f>
       </c>
       <c r="V193" s="3">
-        <f>IF($K193="","",(U193-X193)/J193*100)</f>
+        <f>IF($K193="","",(U193-AB193)/J193*100)</f>
       </c>
       <c r="W193" s="3">
         <f>IF($K193="","",M193-T193)</f>
       </c>
-      <c r="Y193" s="3">
-        <f>IF($K193="","",U193-X193)</f>
-      </c>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC193" s="3">
+        <f>IF($K193="","",U193-AB193)</f>
+      </c>
+    </row>
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="J194" s="3"/>
@@ -9083,16 +9107,16 @@
         <f>IF($K194="","",L194-M194-N194-Q194-R194-S194)</f>
       </c>
       <c r="V194" s="3">
-        <f>IF($K194="","",(U194-X194)/J194*100)</f>
+        <f>IF($K194="","",(U194-AB194)/J194*100)</f>
       </c>
       <c r="W194" s="3">
         <f>IF($K194="","",M194-T194)</f>
       </c>
-      <c r="Y194" s="3">
-        <f>IF($K194="","",U194-X194)</f>
-      </c>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC194" s="3">
+        <f>IF($K194="","",U194-AB194)</f>
+      </c>
+    </row>
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="J195" s="3"/>
@@ -9126,16 +9150,16 @@
         <f>IF($K195="","",L195-M195-N195-Q195-R195-S195)</f>
       </c>
       <c r="V195" s="3">
-        <f>IF($K195="","",(U195-X195)/J195*100)</f>
+        <f>IF($K195="","",(U195-AB195)/J195*100)</f>
       </c>
       <c r="W195" s="3">
         <f>IF($K195="","",M195-T195)</f>
       </c>
-      <c r="Y195" s="3">
-        <f>IF($K195="","",U195-X195)</f>
-      </c>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC195" s="3">
+        <f>IF($K195="","",U195-AB195)</f>
+      </c>
+    </row>
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="J196" s="3"/>
@@ -9169,16 +9193,16 @@
         <f>IF($K196="","",L196-M196-N196-Q196-R196-S196)</f>
       </c>
       <c r="V196" s="3">
-        <f>IF($K196="","",(U196-X196)/J196*100)</f>
+        <f>IF($K196="","",(U196-AB196)/J196*100)</f>
       </c>
       <c r="W196" s="3">
         <f>IF($K196="","",M196-T196)</f>
       </c>
-      <c r="Y196" s="3">
-        <f>IF($K196="","",U196-X196)</f>
-      </c>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC196" s="3">
+        <f>IF($K196="","",U196-AB196)</f>
+      </c>
+    </row>
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="J197" s="3"/>
@@ -9212,16 +9236,16 @@
         <f>IF($K197="","",L197-M197-N197-Q197-R197-S197)</f>
       </c>
       <c r="V197" s="3">
-        <f>IF($K197="","",(U197-X197)/J197*100)</f>
+        <f>IF($K197="","",(U197-AB197)/J197*100)</f>
       </c>
       <c r="W197" s="3">
         <f>IF($K197="","",M197-T197)</f>
       </c>
-      <c r="Y197" s="3">
-        <f>IF($K197="","",U197-X197)</f>
-      </c>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC197" s="3">
+        <f>IF($K197="","",U197-AB197)</f>
+      </c>
+    </row>
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="J198" s="3"/>
@@ -9255,16 +9279,16 @@
         <f>IF($K198="","",L198-M198-N198-Q198-R198-S198)</f>
       </c>
       <c r="V198" s="3">
-        <f>IF($K198="","",(U198-X198)/J198*100)</f>
+        <f>IF($K198="","",(U198-AB198)/J198*100)</f>
       </c>
       <c r="W198" s="3">
         <f>IF($K198="","",M198-T198)</f>
       </c>
-      <c r="Y198" s="3">
-        <f>IF($K198="","",U198-X198)</f>
-      </c>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC198" s="3">
+        <f>IF($K198="","",U198-AB198)</f>
+      </c>
+    </row>
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="J199" s="3"/>
@@ -9298,16 +9322,16 @@
         <f>IF($K199="","",L199-M199-N199-Q199-R199-S199)</f>
       </c>
       <c r="V199" s="3">
-        <f>IF($K199="","",(U199-X199)/J199*100)</f>
+        <f>IF($K199="","",(U199-AB199)/J199*100)</f>
       </c>
       <c r="W199" s="3">
         <f>IF($K199="","",M199-T199)</f>
       </c>
-      <c r="Y199" s="3">
-        <f>IF($K199="","",U199-X199)</f>
-      </c>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC199" s="3">
+        <f>IF($K199="","",U199-AB199)</f>
+      </c>
+    </row>
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="J200" s="3"/>
@@ -9341,16 +9365,16 @@
         <f>IF($K200="","",L200-M200-N200-Q200-R200-S200)</f>
       </c>
       <c r="V200" s="3">
-        <f>IF($K200="","",(U200-X200)/J200*100)</f>
+        <f>IF($K200="","",(U200-AB200)/J200*100)</f>
       </c>
       <c r="W200" s="3">
         <f>IF($K200="","",M200-T200)</f>
       </c>
-      <c r="Y200" s="3">
-        <f>IF($K200="","",U200-X200)</f>
-      </c>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC200" s="3">
+        <f>IF($K200="","",U200-AB200)</f>
+      </c>
+    </row>
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="J201" s="3"/>
@@ -9384,16 +9408,16 @@
         <f>IF($K201="","",L201-M201-N201-Q201-R201-S201)</f>
       </c>
       <c r="V201" s="3">
-        <f>IF($K201="","",(U201-X201)/J201*100)</f>
+        <f>IF($K201="","",(U201-AB201)/J201*100)</f>
       </c>
       <c r="W201" s="3">
         <f>IF($K201="","",M201-T201)</f>
       </c>
-      <c r="Y201" s="3">
-        <f>IF($K201="","",U201-X201)</f>
-      </c>
-    </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC201" s="3">
+        <f>IF($K201="","",U201-AB201)</f>
+      </c>
+    </row>
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="J202" s="3"/>
@@ -9427,18 +9451,18 @@
         <f>IF($K202="","",L202-M202-N202-Q202-R202-S202)</f>
       </c>
       <c r="V202" s="3">
-        <f>IF($K202="","",(U202-X202)/J202*100)</f>
+        <f>IF($K202="","",(U202-AB202)/J202*100)</f>
       </c>
       <c r="W202" s="3">
         <f>IF($K202="","",M202-T202)</f>
       </c>
-      <c r="Y202" s="3">
-        <f>IF($K202="","",U202-X202)</f>
-      </c>
-    </row>
-    <row r="203" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC202" s="3">
+        <f>IF($K202="","",U202-AB202)</f>
+      </c>
+    </row>
+    <row r="203" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -9487,7 +9511,7 @@
         <f>SUM(U2:U202)</f>
       </c>
       <c r="V203" s="6">
-        <f>IFERROR((U203-X203)/J203*100,0)</f>
+        <f>IFERROR((U203-AB203)/J203*100,0)</f>
       </c>
       <c r="W203" s="6">
         <f>SUM(W2:W202)</f>
@@ -9498,11 +9522,23 @@
       <c r="Y203" s="6">
         <f>SUM(Y2:Y202)</f>
       </c>
-      <c r="Z203" s="4"/>
-      <c r="AA203" s="4"/>
-      <c r="AB203" s="4"/>
-      <c r="AC203" s="4"/>
+      <c r="Z203" s="6">
+        <f>SUM(Z2:Z202)</f>
+      </c>
+      <c r="AA203" s="6">
+        <f>SUM(AA2:AA202)</f>
+      </c>
+      <c r="AB203" s="6">
+        <f>SUM(AB2:AB202)</f>
+      </c>
+      <c r="AC203" s="6">
+        <f>SUM(AC2:AC202)</f>
+      </c>
       <c r="AD203" s="4"/>
+      <c r="AE203" s="4"/>
+      <c r="AF203" s="4"/>
+      <c r="AG203" s="4"/>
+      <c r="AH203" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
